--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,9 @@
     <t>['16', '45+5']</t>
   </si>
   <si>
+    <t>['23']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -829,9 +832,6 @@
     <t>['45+2']</t>
   </si>
   <si>
-    <t>['23']</t>
-  </si>
-  <si>
     <t>['9']</t>
   </si>
   <si>
@@ -899,6 +899,12 @@
   </si>
   <si>
     <t>['9', '83']</t>
+  </si>
+  <si>
+    <t>['1']</t>
+  </si>
+  <si>
+    <t>['11', '63']</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1722,7 +1728,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2546,7 +2552,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2752,7 +2758,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2958,7 +2964,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3164,7 +3170,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3370,7 +3376,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3576,7 +3582,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3654,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ12">
         <v>0.88</v>
@@ -3782,7 +3788,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -3988,7 +3994,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4069,7 +4075,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ14">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4194,7 +4200,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4400,7 +4406,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4606,7 +4612,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4687,7 +4693,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4812,7 +4818,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5096,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ19">
         <v>1.75</v>
@@ -5430,7 +5436,7 @@
         <v>91</v>
       </c>
       <c r="P21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q21">
         <v>2.85</v>
@@ -5636,7 +5642,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5842,7 +5848,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6048,7 +6054,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6254,7 +6260,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6666,7 +6672,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7284,7 +7290,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7490,7 +7496,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8108,7 +8114,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8186,10 +8192,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ34">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR34">
         <v>0.72</v>
@@ -8314,7 +8320,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8520,7 +8526,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8726,7 +8732,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9013,7 +9019,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ38">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>2.66</v>
@@ -9138,7 +9144,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9344,7 +9350,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9422,7 +9428,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ40">
         <v>1.3</v>
@@ -9756,7 +9762,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9962,7 +9968,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10168,7 +10174,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10580,7 +10586,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10864,7 +10870,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ47">
         <v>0.5</v>
@@ -11198,7 +11204,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11610,7 +11616,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11691,7 +11697,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ51">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR51">
         <v>1.43</v>
@@ -11816,7 +11822,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12022,7 +12028,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12640,7 +12646,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12846,7 +12852,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13133,7 +13139,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13258,7 +13264,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13464,7 +13470,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13670,7 +13676,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13876,7 +13882,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14082,7 +14088,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14288,7 +14294,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14366,7 +14372,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ64">
         <v>1.22</v>
@@ -14494,7 +14500,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14906,7 +14912,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15190,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ68">
         <v>0.44</v>
@@ -15318,7 +15324,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15524,7 +15530,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15730,7 +15736,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -15811,7 +15817,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ71">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR71">
         <v>1.33</v>
@@ -16348,7 +16354,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16426,7 +16432,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ74">
         <v>0.5600000000000001</v>
@@ -16966,7 +16972,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17172,7 +17178,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17584,7 +17590,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17790,7 +17796,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17996,7 +18002,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18077,7 +18083,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ82">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR82">
         <v>1.45</v>
@@ -18202,7 +18208,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18486,7 +18492,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ84">
         <v>1.11</v>
@@ -18614,7 +18620,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18695,7 +18701,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ85">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -18820,7 +18826,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19026,7 +19032,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19232,7 +19238,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19850,7 +19856,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20056,7 +20062,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20262,7 +20268,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q93">
         <v>2.9</v>
@@ -20343,7 +20349,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ93">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
         <v>1.31</v>
@@ -20546,7 +20552,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ94">
         <v>0.63</v>
@@ -20674,7 +20680,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20880,7 +20886,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21498,7 +21504,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21910,7 +21916,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22116,7 +22122,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22322,7 +22328,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22400,7 +22406,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ103">
         <v>0.5600000000000001</v>
@@ -22528,7 +22534,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>271</v>
+        <v>209</v>
       </c>
       <c r="Q104">
         <v>3.2</v>
@@ -23227,7 +23233,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ107">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR107">
         <v>1.87</v>
@@ -23845,7 +23851,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ110">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR110">
         <v>1.36</v>
@@ -24048,7 +24054,7 @@
         <v>2.33</v>
       </c>
       <c r="AP111">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ111">
         <v>2</v>
@@ -24794,7 +24800,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25000,7 +25006,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -26442,7 +26448,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -27138,7 +27144,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ126">
         <v>1.22</v>
@@ -27884,7 +27890,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28377,7 +28383,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ132">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28580,7 +28586,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ133">
         <v>0.75</v>
@@ -29201,7 +29207,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ136">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -30228,7 +30234,7 @@
         <v>0.71</v>
       </c>
       <c r="AP141">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ141">
         <v>0.67</v>
@@ -31180,7 +31186,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31467,7 +31473,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR147">
         <v>1.24</v>
@@ -31592,7 +31598,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32085,7 +32091,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ150">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR150">
         <v>1.84</v>
@@ -32288,7 +32294,7 @@
         <v>3</v>
       </c>
       <c r="AP151">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ151">
         <v>3</v>
@@ -32906,7 +32912,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ154">
         <v>0.63</v>
@@ -33446,7 +33452,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -34839,6 +34845,418 @@
       </c>
       <c r="BP163">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7516455</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45668.3125</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>80</v>
+      </c>
+      <c r="H164" t="s">
+        <v>76</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164" t="s">
+        <v>91</v>
+      </c>
+      <c r="P164" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q164">
+        <v>3.6</v>
+      </c>
+      <c r="R164">
+        <v>2.1</v>
+      </c>
+      <c r="S164">
+        <v>2.75</v>
+      </c>
+      <c r="T164">
+        <v>1.36</v>
+      </c>
+      <c r="U164">
+        <v>2.85</v>
+      </c>
+      <c r="V164">
+        <v>2.65</v>
+      </c>
+      <c r="W164">
+        <v>1.42</v>
+      </c>
+      <c r="X164">
+        <v>6.25</v>
+      </c>
+      <c r="Y164">
+        <v>1.09</v>
+      </c>
+      <c r="Z164">
+        <v>3.11</v>
+      </c>
+      <c r="AA164">
+        <v>3.44</v>
+      </c>
+      <c r="AB164">
+        <v>2.22</v>
+      </c>
+      <c r="AC164">
+        <v>1.03</v>
+      </c>
+      <c r="AD164">
+        <v>10.65</v>
+      </c>
+      <c r="AE164">
+        <v>1.27</v>
+      </c>
+      <c r="AF164">
+        <v>3.61</v>
+      </c>
+      <c r="AG164">
+        <v>1.83</v>
+      </c>
+      <c r="AH164">
+        <v>1.93</v>
+      </c>
+      <c r="AI164">
+        <v>1.65</v>
+      </c>
+      <c r="AJ164">
+        <v>2.1</v>
+      </c>
+      <c r="AK164">
+        <v>1.65</v>
+      </c>
+      <c r="AL164">
+        <v>1.25</v>
+      </c>
+      <c r="AM164">
+        <v>1.35</v>
+      </c>
+      <c r="AN164">
+        <v>0.75</v>
+      </c>
+      <c r="AO164">
+        <v>2</v>
+      </c>
+      <c r="AP164">
+        <v>0.67</v>
+      </c>
+      <c r="AQ164">
+        <v>2.11</v>
+      </c>
+      <c r="AR164">
+        <v>1.61</v>
+      </c>
+      <c r="AS164">
+        <v>1.27</v>
+      </c>
+      <c r="AT164">
+        <v>2.88</v>
+      </c>
+      <c r="AU164">
+        <v>2</v>
+      </c>
+      <c r="AV164">
+        <v>4</v>
+      </c>
+      <c r="AW164">
+        <v>6</v>
+      </c>
+      <c r="AX164">
+        <v>9</v>
+      </c>
+      <c r="AY164">
+        <v>10</v>
+      </c>
+      <c r="AZ164">
+        <v>17</v>
+      </c>
+      <c r="BA164">
+        <v>5</v>
+      </c>
+      <c r="BB164">
+        <v>3</v>
+      </c>
+      <c r="BC164">
+        <v>8</v>
+      </c>
+      <c r="BD164">
+        <v>2.32</v>
+      </c>
+      <c r="BE164">
+        <v>6.4</v>
+      </c>
+      <c r="BF164">
+        <v>1.74</v>
+      </c>
+      <c r="BG164">
+        <v>1.33</v>
+      </c>
+      <c r="BH164">
+        <v>2.95</v>
+      </c>
+      <c r="BI164">
+        <v>1.57</v>
+      </c>
+      <c r="BJ164">
+        <v>2.2</v>
+      </c>
+      <c r="BK164">
+        <v>1.94</v>
+      </c>
+      <c r="BL164">
+        <v>1.76</v>
+      </c>
+      <c r="BM164">
+        <v>2.45</v>
+      </c>
+      <c r="BN164">
+        <v>1.48</v>
+      </c>
+      <c r="BO164">
+        <v>3.15</v>
+      </c>
+      <c r="BP164">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7516454</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45668.41666666666</v>
+      </c>
+      <c r="F165">
+        <v>19</v>
+      </c>
+      <c r="G165" t="s">
+        <v>87</v>
+      </c>
+      <c r="H165" t="s">
+        <v>77</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="K165">
+        <v>2</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>2</v>
+      </c>
+      <c r="N165">
+        <v>3</v>
+      </c>
+      <c r="O165" t="s">
+        <v>209</v>
+      </c>
+      <c r="P165" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q165">
+        <v>3.6</v>
+      </c>
+      <c r="R165">
+        <v>2.17</v>
+      </c>
+      <c r="S165">
+        <v>2.82</v>
+      </c>
+      <c r="T165">
+        <v>1.36</v>
+      </c>
+      <c r="U165">
+        <v>2.89</v>
+      </c>
+      <c r="V165">
+        <v>2.65</v>
+      </c>
+      <c r="W165">
+        <v>1.42</v>
+      </c>
+      <c r="X165">
+        <v>6.5</v>
+      </c>
+      <c r="Y165">
+        <v>1.08</v>
+      </c>
+      <c r="Z165">
+        <v>2.96</v>
+      </c>
+      <c r="AA165">
+        <v>3.43</v>
+      </c>
+      <c r="AB165">
+        <v>2.3</v>
+      </c>
+      <c r="AC165">
+        <v>1.03</v>
+      </c>
+      <c r="AD165">
+        <v>10.65</v>
+      </c>
+      <c r="AE165">
+        <v>1.27</v>
+      </c>
+      <c r="AF165">
+        <v>3.61</v>
+      </c>
+      <c r="AG165">
+        <v>1.83</v>
+      </c>
+      <c r="AH165">
+        <v>1.93</v>
+      </c>
+      <c r="AI165">
+        <v>1.67</v>
+      </c>
+      <c r="AJ165">
+        <v>2.07</v>
+      </c>
+      <c r="AK165">
+        <v>1.63</v>
+      </c>
+      <c r="AL165">
+        <v>1.31</v>
+      </c>
+      <c r="AM165">
+        <v>1.38</v>
+      </c>
+      <c r="AN165">
+        <v>0.78</v>
+      </c>
+      <c r="AO165">
+        <v>1.13</v>
+      </c>
+      <c r="AP165">
+        <v>0.7</v>
+      </c>
+      <c r="AQ165">
+        <v>1.33</v>
+      </c>
+      <c r="AR165">
+        <v>1.23</v>
+      </c>
+      <c r="AS165">
+        <v>1.1</v>
+      </c>
+      <c r="AT165">
+        <v>2.33</v>
+      </c>
+      <c r="AU165">
+        <v>5</v>
+      </c>
+      <c r="AV165">
+        <v>5</v>
+      </c>
+      <c r="AW165">
+        <v>10</v>
+      </c>
+      <c r="AX165">
+        <v>10</v>
+      </c>
+      <c r="AY165">
+        <v>16</v>
+      </c>
+      <c r="AZ165">
+        <v>15</v>
+      </c>
+      <c r="BA165">
+        <v>3</v>
+      </c>
+      <c r="BB165">
+        <v>4</v>
+      </c>
+      <c r="BC165">
+        <v>7</v>
+      </c>
+      <c r="BD165">
+        <v>2.23</v>
+      </c>
+      <c r="BE165">
+        <v>6.4</v>
+      </c>
+      <c r="BF165">
+        <v>1.78</v>
+      </c>
+      <c r="BG165">
+        <v>1.32</v>
+      </c>
+      <c r="BH165">
+        <v>3.05</v>
+      </c>
+      <c r="BI165">
+        <v>1.55</v>
+      </c>
+      <c r="BJ165">
+        <v>2.25</v>
+      </c>
+      <c r="BK165">
+        <v>1.9</v>
+      </c>
+      <c r="BL165">
+        <v>1.78</v>
+      </c>
+      <c r="BM165">
+        <v>2.4</v>
+      </c>
+      <c r="BN165">
+        <v>1.49</v>
+      </c>
+      <c r="BO165">
+        <v>3.15</v>
+      </c>
+      <c r="BP165">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="299">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,9 @@
     <t>['23']</t>
   </si>
   <si>
+    <t>['32', '40']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -905,6 +908,9 @@
   </si>
   <si>
     <t>['11', '63']</t>
+  </si>
+  <si>
+    <t>['56']</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1728,7 +1734,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2424,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ6">
         <v>0.44</v>
@@ -2552,7 +2558,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2758,7 +2764,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2964,7 +2970,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3170,7 +3176,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3376,7 +3382,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3582,7 +3588,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3788,7 +3794,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -3994,7 +4000,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4200,7 +4206,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4281,7 +4287,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4406,7 +4412,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4484,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ16">
         <v>0.63</v>
@@ -4612,7 +4618,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4818,7 +4824,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -4899,7 +4905,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ18">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5436,7 +5442,7 @@
         <v>91</v>
       </c>
       <c r="P21" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q21">
         <v>2.85</v>
@@ -5514,7 +5520,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21">
         <v>1.3</v>
@@ -5642,7 +5648,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5848,7 +5854,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6054,7 +6060,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6260,7 +6266,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6547,7 +6553,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ26">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR26">
         <v>1.44</v>
@@ -6672,7 +6678,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7165,7 +7171,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ29">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR29">
         <v>1.71</v>
@@ -7290,7 +7296,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7496,7 +7502,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7986,7 +7992,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ33">
         <v>0.88</v>
@@ -8114,7 +8120,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8320,7 +8326,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8398,7 +8404,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35">
         <v>0.5600000000000001</v>
@@ -8526,7 +8532,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8732,7 +8738,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9144,7 +9150,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9350,7 +9356,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9762,7 +9768,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9968,7 +9974,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10174,7 +10180,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10586,7 +10592,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10873,7 +10879,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ47">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR47">
         <v>0.7</v>
@@ -11204,7 +11210,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11616,7 +11622,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11822,7 +11828,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11903,7 +11909,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ52">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR52">
         <v>1.43</v>
@@ -12028,7 +12034,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12106,7 +12112,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ53">
         <v>1.3</v>
@@ -12646,7 +12652,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12724,7 +12730,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ56">
         <v>1.11</v>
@@ -12852,7 +12858,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13264,7 +13270,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13470,7 +13476,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13676,7 +13682,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13882,7 +13888,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14088,7 +14094,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14294,7 +14300,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14500,7 +14506,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14787,7 +14793,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ66">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -14912,7 +14918,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15324,7 +15330,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15530,7 +15536,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15736,7 +15742,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16023,7 +16029,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ72">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16354,7 +16360,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16972,7 +16978,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17178,7 +17184,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17256,7 +17262,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ78">
         <v>0.25</v>
@@ -17462,7 +17468,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17590,7 +17596,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17796,7 +17802,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18002,7 +18008,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18208,7 +18214,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18620,7 +18626,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18826,7 +18832,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19032,7 +19038,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19238,7 +19244,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19525,7 +19531,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR89">
         <v>1.9</v>
@@ -19856,7 +19862,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20062,7 +20068,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20268,7 +20274,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q93">
         <v>2.9</v>
@@ -20346,7 +20352,7 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20680,7 +20686,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20758,7 +20764,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ95">
         <v>1.75</v>
@@ -20886,7 +20892,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21379,7 +21385,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ98">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21504,7 +21510,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21916,7 +21922,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22122,7 +22128,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22203,7 +22209,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ102">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR102">
         <v>1.28</v>
@@ -22328,7 +22334,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22740,7 +22746,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23152,7 +23158,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23770,7 +23776,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23976,7 +23982,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24388,7 +24394,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24672,7 +24678,7 @@
         <v>2.2</v>
       </c>
       <c r="AP114">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ114">
         <v>1.75</v>
@@ -24800,7 +24806,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25006,7 +25012,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25087,7 +25093,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ116">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR116">
         <v>1.6</v>
@@ -25212,7 +25218,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25290,7 +25296,7 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ117">
         <v>0.67</v>
@@ -25624,7 +25630,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25911,7 +25917,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ120">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR120">
         <v>1.52</v>
@@ -26036,7 +26042,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26242,7 +26248,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26448,7 +26454,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26860,7 +26866,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27066,7 +27072,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27272,7 +27278,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27478,7 +27484,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27890,7 +27896,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28174,7 +28180,7 @@
         <v>2.43</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ131">
         <v>2</v>
@@ -28589,7 +28595,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ133">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR133">
         <v>1.67</v>
@@ -28714,7 +28720,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -28792,7 +28798,7 @@
         <v>3</v>
       </c>
       <c r="AP134">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ134">
         <v>3</v>
@@ -30156,7 +30162,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30774,7 +30780,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -30980,7 +30986,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31186,7 +31192,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31470,7 +31476,7 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ147">
         <v>2.11</v>
@@ -31598,7 +31604,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31676,10 +31682,10 @@
         <v>0.71</v>
       </c>
       <c r="AP148">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ148">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR148">
         <v>1.58</v>
@@ -32216,7 +32222,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32503,7 +32509,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ152">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR152">
         <v>1.63</v>
@@ -32628,7 +32634,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32834,7 +32840,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33246,7 +33252,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33452,7 +33458,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33658,7 +33664,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34070,7 +34076,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34276,7 +34282,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34894,7 +34900,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35100,7 +35106,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35257,6 +35263,418 @@
       </c>
       <c r="BP165">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7516452</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45668.54166666666</v>
+      </c>
+      <c r="F166">
+        <v>19</v>
+      </c>
+      <c r="G166" t="s">
+        <v>84</v>
+      </c>
+      <c r="H166" t="s">
+        <v>78</v>
+      </c>
+      <c r="I166">
+        <v>2</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>2</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>3</v>
+      </c>
+      <c r="O166" t="s">
+        <v>210</v>
+      </c>
+      <c r="P166" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q166">
+        <v>2</v>
+      </c>
+      <c r="R166">
+        <v>2.3</v>
+      </c>
+      <c r="S166">
+        <v>5.5</v>
+      </c>
+      <c r="T166">
+        <v>1.33</v>
+      </c>
+      <c r="U166">
+        <v>3</v>
+      </c>
+      <c r="V166">
+        <v>2.55</v>
+      </c>
+      <c r="W166">
+        <v>1.45</v>
+      </c>
+      <c r="X166">
+        <v>5.75</v>
+      </c>
+      <c r="Y166">
+        <v>1.1</v>
+      </c>
+      <c r="Z166">
+        <v>1.48</v>
+      </c>
+      <c r="AA166">
+        <v>4.49</v>
+      </c>
+      <c r="AB166">
+        <v>6.06</v>
+      </c>
+      <c r="AC166">
+        <v>1.04</v>
+      </c>
+      <c r="AD166">
+        <v>15</v>
+      </c>
+      <c r="AE166">
+        <v>1.21</v>
+      </c>
+      <c r="AF166">
+        <v>4.22</v>
+      </c>
+      <c r="AG166">
+        <v>1.69</v>
+      </c>
+      <c r="AH166">
+        <v>2.12</v>
+      </c>
+      <c r="AI166">
+        <v>1.8</v>
+      </c>
+      <c r="AJ166">
+        <v>1.9</v>
+      </c>
+      <c r="AK166">
+        <v>1.12</v>
+      </c>
+      <c r="AL166">
+        <v>1.17</v>
+      </c>
+      <c r="AM166">
+        <v>2.45</v>
+      </c>
+      <c r="AN166">
+        <v>2</v>
+      </c>
+      <c r="AO166">
+        <v>0.5</v>
+      </c>
+      <c r="AP166">
+        <v>2.11</v>
+      </c>
+      <c r="AQ166">
+        <v>0.44</v>
+      </c>
+      <c r="AR166">
+        <v>1.54</v>
+      </c>
+      <c r="AS166">
+        <v>1.08</v>
+      </c>
+      <c r="AT166">
+        <v>2.62</v>
+      </c>
+      <c r="AU166">
+        <v>6</v>
+      </c>
+      <c r="AV166">
+        <v>6</v>
+      </c>
+      <c r="AW166">
+        <v>4</v>
+      </c>
+      <c r="AX166">
+        <v>13</v>
+      </c>
+      <c r="AY166">
+        <v>12</v>
+      </c>
+      <c r="AZ166">
+        <v>23</v>
+      </c>
+      <c r="BA166">
+        <v>4</v>
+      </c>
+      <c r="BB166">
+        <v>12</v>
+      </c>
+      <c r="BC166">
+        <v>16</v>
+      </c>
+      <c r="BD166">
+        <v>1.45</v>
+      </c>
+      <c r="BE166">
+        <v>6.75</v>
+      </c>
+      <c r="BF166">
+        <v>3.15</v>
+      </c>
+      <c r="BG166">
+        <v>1.35</v>
+      </c>
+      <c r="BH166">
+        <v>2.9</v>
+      </c>
+      <c r="BI166">
+        <v>1.6</v>
+      </c>
+      <c r="BJ166">
+        <v>2.17</v>
+      </c>
+      <c r="BK166">
+        <v>1.97</v>
+      </c>
+      <c r="BL166">
+        <v>1.72</v>
+      </c>
+      <c r="BM166">
+        <v>2.5</v>
+      </c>
+      <c r="BN166">
+        <v>1.46</v>
+      </c>
+      <c r="BO166">
+        <v>3.3</v>
+      </c>
+      <c r="BP166">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7516453</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45669.3125</v>
+      </c>
+      <c r="F167">
+        <v>19</v>
+      </c>
+      <c r="G167" t="s">
+        <v>74</v>
+      </c>
+      <c r="H167" t="s">
+        <v>75</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>2</v>
+      </c>
+      <c r="O167" t="s">
+        <v>178</v>
+      </c>
+      <c r="P167" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q167">
+        <v>3.3</v>
+      </c>
+      <c r="R167">
+        <v>2.15</v>
+      </c>
+      <c r="S167">
+        <v>3.25</v>
+      </c>
+      <c r="T167">
+        <v>1.44</v>
+      </c>
+      <c r="U167">
+        <v>3</v>
+      </c>
+      <c r="V167">
+        <v>2.95</v>
+      </c>
+      <c r="W167">
+        <v>1.45</v>
+      </c>
+      <c r="X167">
+        <v>8</v>
+      </c>
+      <c r="Y167">
+        <v>1.11</v>
+      </c>
+      <c r="Z167">
+        <v>2.85</v>
+      </c>
+      <c r="AA167">
+        <v>3.38</v>
+      </c>
+      <c r="AB167">
+        <v>2.49</v>
+      </c>
+      <c r="AC167">
+        <v>1.03</v>
+      </c>
+      <c r="AD167">
+        <v>10.65</v>
+      </c>
+      <c r="AE167">
+        <v>1.27</v>
+      </c>
+      <c r="AF167">
+        <v>3.61</v>
+      </c>
+      <c r="AG167">
+        <v>1.89</v>
+      </c>
+      <c r="AH167">
+        <v>1.94</v>
+      </c>
+      <c r="AI167">
+        <v>1.68</v>
+      </c>
+      <c r="AJ167">
+        <v>2.15</v>
+      </c>
+      <c r="AK167">
+        <v>1.53</v>
+      </c>
+      <c r="AL167">
+        <v>1.35</v>
+      </c>
+      <c r="AM167">
+        <v>1.52</v>
+      </c>
+      <c r="AN167">
+        <v>1.33</v>
+      </c>
+      <c r="AO167">
+        <v>0.75</v>
+      </c>
+      <c r="AP167">
+        <v>1.3</v>
+      </c>
+      <c r="AQ167">
+        <v>0.78</v>
+      </c>
+      <c r="AR167">
+        <v>1.22</v>
+      </c>
+      <c r="AS167">
+        <v>1.09</v>
+      </c>
+      <c r="AT167">
+        <v>2.31</v>
+      </c>
+      <c r="AU167">
+        <v>5</v>
+      </c>
+      <c r="AV167">
+        <v>3</v>
+      </c>
+      <c r="AW167">
+        <v>5</v>
+      </c>
+      <c r="AX167">
+        <v>4</v>
+      </c>
+      <c r="AY167">
+        <v>10</v>
+      </c>
+      <c r="AZ167">
+        <v>7</v>
+      </c>
+      <c r="BA167">
+        <v>2</v>
+      </c>
+      <c r="BB167">
+        <v>6</v>
+      </c>
+      <c r="BC167">
+        <v>8</v>
+      </c>
+      <c r="BD167">
+        <v>2.12</v>
+      </c>
+      <c r="BE167">
+        <v>6.4</v>
+      </c>
+      <c r="BF167">
+        <v>1.88</v>
+      </c>
+      <c r="BG167">
+        <v>1.37</v>
+      </c>
+      <c r="BH167">
+        <v>2.8</v>
+      </c>
+      <c r="BI167">
+        <v>1.63</v>
+      </c>
+      <c r="BJ167">
+        <v>2.12</v>
+      </c>
+      <c r="BK167">
+        <v>1.98</v>
+      </c>
+      <c r="BL167">
+        <v>1.72</v>
+      </c>
+      <c r="BM167">
+        <v>2.55</v>
+      </c>
+      <c r="BN167">
+        <v>1.44</v>
+      </c>
+      <c r="BO167">
+        <v>3.4</v>
+      </c>
+      <c r="BP167">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="301">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -649,6 +649,9 @@
     <t>['32', '40']</t>
   </si>
   <si>
+    <t>['21', '52', '64', '70', '87']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -911,6 +914,9 @@
   </si>
   <si>
     <t>['56']</t>
+  </si>
+  <si>
+    <t>['42', '59']</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP167"/>
+  <dimension ref="A1:BP170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1734,7 +1740,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2227,7 +2233,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ5">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2558,7 +2564,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2764,7 +2770,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2970,7 +2976,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3176,7 +3182,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3382,7 +3388,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3588,7 +3594,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3794,7 +3800,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4000,7 +4006,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4206,7 +4212,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4284,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ15">
         <v>0.78</v>
@@ -4412,7 +4418,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4493,7 +4499,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4618,7 +4624,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4696,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17">
         <v>2.11</v>
@@ -4824,7 +4830,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5442,7 +5448,7 @@
         <v>91</v>
       </c>
       <c r="P21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q21">
         <v>2.85</v>
@@ -5648,7 +5654,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5854,7 +5860,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -5935,7 +5941,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ23">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR23">
         <v>0.96</v>
@@ -6060,7 +6066,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6266,7 +6272,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6678,7 +6684,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7296,7 +7302,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7502,7 +7508,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7580,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ31">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR31">
         <v>1.45</v>
@@ -8120,7 +8126,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8326,7 +8332,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8532,7 +8538,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8738,7 +8744,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9150,7 +9156,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9356,7 +9362,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9768,7 +9774,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9846,7 +9852,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
         <v>1.22</v>
@@ -9974,7 +9980,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10055,7 +10061,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ43">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR43">
         <v>1.43</v>
@@ -10180,7 +10186,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10592,7 +10598,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10670,7 +10676,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1.11</v>
@@ -11210,7 +11216,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11497,7 +11503,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ50">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR50">
         <v>1.45</v>
@@ -11622,7 +11628,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11828,7 +11834,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12034,7 +12040,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12524,7 +12530,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ55">
         <v>0.44</v>
@@ -12652,7 +12658,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12858,7 +12864,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13270,7 +13276,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13476,7 +13482,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13682,7 +13688,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13760,7 +13766,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -13888,7 +13894,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13969,7 +13975,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ62">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14094,7 +14100,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14300,7 +14306,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14506,7 +14512,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14587,7 +14593,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14918,7 +14924,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15330,7 +15336,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15408,7 +15414,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ69">
         <v>1.11</v>
@@ -15536,7 +15542,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15742,7 +15748,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16232,7 +16238,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ73">
         <v>1.22</v>
@@ -16360,7 +16366,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16644,7 +16650,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>1.11</v>
@@ -16978,7 +16984,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17184,7 +17190,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17596,7 +17602,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17802,7 +17808,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18008,7 +18014,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18214,7 +18220,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18626,7 +18632,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18832,7 +18838,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19038,7 +19044,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19116,7 +19122,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ87">
         <v>1</v>
@@ -19244,7 +19250,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19325,7 +19331,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ88">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19734,7 +19740,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ90">
         <v>1.3</v>
@@ -19862,7 +19868,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20068,7 +20074,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20146,7 +20152,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ92">
         <v>0.67</v>
@@ -20274,7 +20280,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q93">
         <v>2.9</v>
@@ -20561,7 +20567,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ94">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -20686,7 +20692,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20892,7 +20898,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21510,7 +21516,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21588,7 +21594,7 @@
         <v>2.2</v>
       </c>
       <c r="AP99">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
         <v>2</v>
@@ -21797,7 +21803,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ100">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR100">
         <v>1.54</v>
@@ -21922,7 +21928,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22128,7 +22134,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22334,7 +22340,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22746,7 +22752,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23158,7 +23164,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23648,7 +23654,7 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ109">
         <v>1.22</v>
@@ -23776,7 +23782,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23982,7 +23988,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24266,7 +24272,7 @@
         <v>1.17</v>
       </c>
       <c r="AP112">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ112">
         <v>1.11</v>
@@ -24394,7 +24400,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24806,7 +24812,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25012,7 +25018,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25218,7 +25224,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25502,10 +25508,10 @@
         <v>0.4</v>
       </c>
       <c r="AP118">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25630,7 +25636,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26042,7 +26048,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26248,7 +26254,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26326,7 +26332,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ122">
         <v>0.67</v>
@@ -26454,7 +26460,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26866,7 +26872,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27072,7 +27078,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27278,7 +27284,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27484,7 +27490,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27562,7 +27568,7 @@
         <v>2</v>
       </c>
       <c r="AP128">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ128">
         <v>1.75</v>
@@ -27771,7 +27777,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ129">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -27896,7 +27902,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -27977,7 +27983,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ130">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR130">
         <v>1.76</v>
@@ -28720,7 +28726,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29004,7 +29010,7 @@
         <v>0.33</v>
       </c>
       <c r="AP135">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ135">
         <v>0.25</v>
@@ -29210,7 +29216,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ136">
         <v>1.33</v>
@@ -30162,7 +30168,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30780,7 +30786,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -30986,7 +30992,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31192,7 +31198,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31604,7 +31610,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31888,10 +31894,10 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ149">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR149">
         <v>1.44</v>
@@ -32222,7 +32228,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32506,7 +32512,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ152">
         <v>0.44</v>
@@ -32634,7 +32640,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32712,7 +32718,7 @@
         <v>1.86</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ153">
         <v>1.75</v>
@@ -32840,7 +32846,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -32921,7 +32927,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ154">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR154">
         <v>1.16</v>
@@ -33252,7 +33258,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33458,7 +33464,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33664,7 +33670,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34076,7 +34082,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34282,7 +34288,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34900,7 +34906,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -34999,16 +35005,16 @@
         <v>4</v>
       </c>
       <c r="AW164">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX164">
+        <v>4</v>
+      </c>
+      <c r="AY164">
         <v>9</v>
       </c>
-      <c r="AY164">
-        <v>10</v>
-      </c>
       <c r="AZ164">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA164">
         <v>5</v>
@@ -35106,7 +35112,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35199,22 +35205,22 @@
         <v>2.33</v>
       </c>
       <c r="AU165">
+        <v>6</v>
+      </c>
+      <c r="AV165">
+        <v>6</v>
+      </c>
+      <c r="AW165">
         <v>5</v>
       </c>
-      <c r="AV165">
-        <v>5</v>
-      </c>
-      <c r="AW165">
-        <v>10</v>
-      </c>
       <c r="AX165">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY165">
         <v>16</v>
       </c>
       <c r="AZ165">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA165">
         <v>3</v>
@@ -35312,7 +35318,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35408,19 +35414,19 @@
         <v>6</v>
       </c>
       <c r="AV166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW166">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AX166">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AY166">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ166">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA166">
         <v>4</v>
@@ -35518,7 +35524,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -35611,7 +35617,7 @@
         <v>2.31</v>
       </c>
       <c r="AU167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV167">
         <v>3</v>
@@ -35626,7 +35632,7 @@
         <v>10</v>
       </c>
       <c r="AZ167">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA167">
         <v>2</v>
@@ -35675,6 +35681,624 @@
       </c>
       <c r="BP167">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7516457</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45669.41666666666</v>
+      </c>
+      <c r="F168">
+        <v>19</v>
+      </c>
+      <c r="G168" t="s">
+        <v>88</v>
+      </c>
+      <c r="H168" t="s">
+        <v>72</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>5</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>5</v>
+      </c>
+      <c r="O168" t="s">
+        <v>211</v>
+      </c>
+      <c r="P168" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q168">
+        <v>2.2</v>
+      </c>
+      <c r="R168">
+        <v>2.4</v>
+      </c>
+      <c r="S168">
+        <v>4.75</v>
+      </c>
+      <c r="T168">
+        <v>1.33</v>
+      </c>
+      <c r="U168">
+        <v>3.6</v>
+      </c>
+      <c r="V168">
+        <v>2.5</v>
+      </c>
+      <c r="W168">
+        <v>1.6</v>
+      </c>
+      <c r="X168">
+        <v>6</v>
+      </c>
+      <c r="Y168">
+        <v>1.16</v>
+      </c>
+      <c r="Z168">
+        <v>1.62</v>
+      </c>
+      <c r="AA168">
+        <v>4.26</v>
+      </c>
+      <c r="AB168">
+        <v>4.71</v>
+      </c>
+      <c r="AC168">
+        <v>1.04</v>
+      </c>
+      <c r="AD168">
+        <v>15</v>
+      </c>
+      <c r="AE168">
+        <v>1.19</v>
+      </c>
+      <c r="AF168">
+        <v>4.5</v>
+      </c>
+      <c r="AG168">
+        <v>1.61</v>
+      </c>
+      <c r="AH168">
+        <v>2.26</v>
+      </c>
+      <c r="AI168">
+        <v>1.66</v>
+      </c>
+      <c r="AJ168">
+        <v>2.2</v>
+      </c>
+      <c r="AK168">
+        <v>1.2</v>
+      </c>
+      <c r="AL168">
+        <v>1.25</v>
+      </c>
+      <c r="AM168">
+        <v>2.35</v>
+      </c>
+      <c r="AN168">
+        <v>1.88</v>
+      </c>
+      <c r="AO168">
+        <v>0.63</v>
+      </c>
+      <c r="AP168">
+        <v>2</v>
+      </c>
+      <c r="AQ168">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR168">
+        <v>1.65</v>
+      </c>
+      <c r="AS168">
+        <v>1.03</v>
+      </c>
+      <c r="AT168">
+        <v>2.68</v>
+      </c>
+      <c r="AU168">
+        <v>7</v>
+      </c>
+      <c r="AV168">
+        <v>3</v>
+      </c>
+      <c r="AW168">
+        <v>4</v>
+      </c>
+      <c r="AX168">
+        <v>7</v>
+      </c>
+      <c r="AY168">
+        <v>17</v>
+      </c>
+      <c r="AZ168">
+        <v>11</v>
+      </c>
+      <c r="BA168">
+        <v>7</v>
+      </c>
+      <c r="BB168">
+        <v>5</v>
+      </c>
+      <c r="BC168">
+        <v>12</v>
+      </c>
+      <c r="BD168">
+        <v>1.49</v>
+      </c>
+      <c r="BE168">
+        <v>6.75</v>
+      </c>
+      <c r="BF168">
+        <v>2.9</v>
+      </c>
+      <c r="BG168">
+        <v>1.3</v>
+      </c>
+      <c r="BH168">
+        <v>3.05</v>
+      </c>
+      <c r="BI168">
+        <v>1.54</v>
+      </c>
+      <c r="BJ168">
+        <v>2.3</v>
+      </c>
+      <c r="BK168">
+        <v>1.9</v>
+      </c>
+      <c r="BL168">
+        <v>1.79</v>
+      </c>
+      <c r="BM168">
+        <v>2.38</v>
+      </c>
+      <c r="BN168">
+        <v>1.5</v>
+      </c>
+      <c r="BO168">
+        <v>3.05</v>
+      </c>
+      <c r="BP168">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7516459</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45669.54166666666</v>
+      </c>
+      <c r="F169">
+        <v>19</v>
+      </c>
+      <c r="G169" t="s">
+        <v>85</v>
+      </c>
+      <c r="H169" t="s">
+        <v>82</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>1</v>
+      </c>
+      <c r="O169" t="s">
+        <v>188</v>
+      </c>
+      <c r="P169" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q169">
+        <v>2</v>
+      </c>
+      <c r="R169">
+        <v>2.55</v>
+      </c>
+      <c r="S169">
+        <v>5.5</v>
+      </c>
+      <c r="T169">
+        <v>1.3</v>
+      </c>
+      <c r="U169">
+        <v>3.75</v>
+      </c>
+      <c r="V169">
+        <v>2.35</v>
+      </c>
+      <c r="W169">
+        <v>1.65</v>
+      </c>
+      <c r="X169">
+        <v>5.5</v>
+      </c>
+      <c r="Y169">
+        <v>1.18</v>
+      </c>
+      <c r="Z169">
+        <v>1.48</v>
+      </c>
+      <c r="AA169">
+        <v>4.49</v>
+      </c>
+      <c r="AB169">
+        <v>6.06</v>
+      </c>
+      <c r="AC169">
+        <v>1.03</v>
+      </c>
+      <c r="AD169">
+        <v>19</v>
+      </c>
+      <c r="AE169">
+        <v>1.15</v>
+      </c>
+      <c r="AF169">
+        <v>5.17</v>
+      </c>
+      <c r="AG169">
+        <v>1.52</v>
+      </c>
+      <c r="AH169">
+        <v>2.45</v>
+      </c>
+      <c r="AI169">
+        <v>1.65</v>
+      </c>
+      <c r="AJ169">
+        <v>2.2</v>
+      </c>
+      <c r="AK169">
+        <v>1.16</v>
+      </c>
+      <c r="AL169">
+        <v>1.22</v>
+      </c>
+      <c r="AM169">
+        <v>2.7</v>
+      </c>
+      <c r="AN169">
+        <v>2.13</v>
+      </c>
+      <c r="AO169">
+        <v>0.63</v>
+      </c>
+      <c r="AP169">
+        <v>2.22</v>
+      </c>
+      <c r="AQ169">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR169">
+        <v>1.48</v>
+      </c>
+      <c r="AS169">
+        <v>1.18</v>
+      </c>
+      <c r="AT169">
+        <v>2.66</v>
+      </c>
+      <c r="AU169">
+        <v>5</v>
+      </c>
+      <c r="AV169">
+        <v>5</v>
+      </c>
+      <c r="AW169">
+        <v>6</v>
+      </c>
+      <c r="AX169">
+        <v>7</v>
+      </c>
+      <c r="AY169">
+        <v>12</v>
+      </c>
+      <c r="AZ169">
+        <v>16</v>
+      </c>
+      <c r="BA169">
+        <v>2</v>
+      </c>
+      <c r="BB169">
+        <v>11</v>
+      </c>
+      <c r="BC169">
+        <v>13</v>
+      </c>
+      <c r="BD169">
+        <v>1.47</v>
+      </c>
+      <c r="BE169">
+        <v>7</v>
+      </c>
+      <c r="BF169">
+        <v>2.95</v>
+      </c>
+      <c r="BG169">
+        <v>1.32</v>
+      </c>
+      <c r="BH169">
+        <v>3.05</v>
+      </c>
+      <c r="BI169">
+        <v>1.55</v>
+      </c>
+      <c r="BJ169">
+        <v>2.28</v>
+      </c>
+      <c r="BK169">
+        <v>1.88</v>
+      </c>
+      <c r="BL169">
+        <v>1.8</v>
+      </c>
+      <c r="BM169">
+        <v>2.4</v>
+      </c>
+      <c r="BN169">
+        <v>1.5</v>
+      </c>
+      <c r="BO169">
+        <v>3.05</v>
+      </c>
+      <c r="BP169">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7516458</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45669.54166666666</v>
+      </c>
+      <c r="F170">
+        <v>19</v>
+      </c>
+      <c r="G170" t="s">
+        <v>83</v>
+      </c>
+      <c r="H170" t="s">
+        <v>70</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <v>2</v>
+      </c>
+      <c r="N170">
+        <v>3</v>
+      </c>
+      <c r="O170" t="s">
+        <v>132</v>
+      </c>
+      <c r="P170" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q170">
+        <v>4.75</v>
+      </c>
+      <c r="R170">
+        <v>2.55</v>
+      </c>
+      <c r="S170">
+        <v>2.1</v>
+      </c>
+      <c r="T170">
+        <v>1.3</v>
+      </c>
+      <c r="U170">
+        <v>3.75</v>
+      </c>
+      <c r="V170">
+        <v>2.35</v>
+      </c>
+      <c r="W170">
+        <v>1.65</v>
+      </c>
+      <c r="X170">
+        <v>5.5</v>
+      </c>
+      <c r="Y170">
+        <v>1.18</v>
+      </c>
+      <c r="Z170">
+        <v>4.75</v>
+      </c>
+      <c r="AA170">
+        <v>4.52</v>
+      </c>
+      <c r="AB170">
+        <v>1.58</v>
+      </c>
+      <c r="AC170">
+        <v>1.02</v>
+      </c>
+      <c r="AD170">
+        <v>21</v>
+      </c>
+      <c r="AE170">
+        <v>1.15</v>
+      </c>
+      <c r="AF170">
+        <v>5.17</v>
+      </c>
+      <c r="AG170">
+        <v>1.52</v>
+      </c>
+      <c r="AH170">
+        <v>2.45</v>
+      </c>
+      <c r="AI170">
+        <v>1.6</v>
+      </c>
+      <c r="AJ170">
+        <v>2.3</v>
+      </c>
+      <c r="AK170">
+        <v>2.45</v>
+      </c>
+      <c r="AL170">
+        <v>1.22</v>
+      </c>
+      <c r="AM170">
+        <v>1.2</v>
+      </c>
+      <c r="AN170">
+        <v>2</v>
+      </c>
+      <c r="AO170">
+        <v>3</v>
+      </c>
+      <c r="AP170">
+        <v>1.78</v>
+      </c>
+      <c r="AQ170">
+        <v>3</v>
+      </c>
+      <c r="AR170">
+        <v>1.59</v>
+      </c>
+      <c r="AS170">
+        <v>1.94</v>
+      </c>
+      <c r="AT170">
+        <v>3.53</v>
+      </c>
+      <c r="AU170">
+        <v>3</v>
+      </c>
+      <c r="AV170">
+        <v>6</v>
+      </c>
+      <c r="AW170">
+        <v>6</v>
+      </c>
+      <c r="AX170">
+        <v>10</v>
+      </c>
+      <c r="AY170">
+        <v>11</v>
+      </c>
+      <c r="AZ170">
+        <v>20</v>
+      </c>
+      <c r="BA170">
+        <v>7</v>
+      </c>
+      <c r="BB170">
+        <v>5</v>
+      </c>
+      <c r="BC170">
+        <v>12</v>
+      </c>
+      <c r="BD170">
+        <v>3.45</v>
+      </c>
+      <c r="BE170">
+        <v>7</v>
+      </c>
+      <c r="BF170">
+        <v>1.35</v>
+      </c>
+      <c r="BG170">
+        <v>1.28</v>
+      </c>
+      <c r="BH170">
+        <v>3.2</v>
+      </c>
+      <c r="BI170">
+        <v>1.49</v>
+      </c>
+      <c r="BJ170">
+        <v>2.4</v>
+      </c>
+      <c r="BK170">
+        <v>1.78</v>
+      </c>
+      <c r="BL170">
+        <v>1.9</v>
+      </c>
+      <c r="BM170">
+        <v>2.2</v>
+      </c>
+      <c r="BN170">
+        <v>1.57</v>
+      </c>
+      <c r="BO170">
+        <v>2.8</v>
+      </c>
+      <c r="BP170">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="304">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -652,6 +652,12 @@
     <t>['21', '52', '64', '70', '87']</t>
   </si>
   <si>
+    <t>['7', '52', '78', '86', '90+3']</t>
+  </si>
+  <si>
+    <t>['1', '44']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -917,6 +923,9 @@
   </si>
   <si>
     <t>['42', '59']</t>
+  </si>
+  <si>
+    <t>['14', '25', '60']</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP170"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1740,7 +1749,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2564,7 +2573,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2770,7 +2779,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2976,7 +2985,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3182,7 +3191,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3388,7 +3397,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3466,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ11">
         <v>3</v>
@@ -3594,7 +3603,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3800,7 +3809,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -3878,10 +3887,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4006,7 +4015,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4212,7 +4221,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4418,7 +4427,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4624,7 +4633,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4830,7 +4839,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5117,7 +5126,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ19">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5448,7 +5457,7 @@
         <v>91</v>
       </c>
       <c r="P21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q21">
         <v>2.85</v>
@@ -5654,7 +5663,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5860,7 +5869,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6066,7 +6075,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6272,7 +6281,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6353,7 +6362,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR25">
         <v>1.86</v>
@@ -6684,7 +6693,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6765,7 +6774,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ27">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -6968,7 +6977,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
         <v>1.11</v>
@@ -7174,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ29">
         <v>0.44</v>
@@ -7302,7 +7311,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7508,7 +7517,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8126,7 +8135,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8332,7 +8341,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8538,7 +8547,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8744,7 +8753,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9156,7 +9165,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9237,7 +9246,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ39">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR39">
         <v>1.4</v>
@@ -9362,7 +9371,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9774,7 +9783,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9980,7 +9989,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10186,7 +10195,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10598,7 +10607,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11088,7 +11097,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ48">
         <v>0.88</v>
@@ -11216,7 +11225,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11628,7 +11637,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11834,7 +11843,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12040,7 +12049,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12324,7 +12333,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ54">
         <v>1.11</v>
@@ -12658,7 +12667,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12864,7 +12873,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13276,7 +13285,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13357,7 +13366,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ59">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR59">
         <v>2.34</v>
@@ -13482,7 +13491,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13688,7 +13697,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13894,7 +13903,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14100,7 +14109,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14181,7 +14190,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ63">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -14306,7 +14315,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14512,7 +14521,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14924,7 +14933,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15002,7 +15011,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ67">
         <v>0.88</v>
@@ -15336,7 +15345,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15542,7 +15551,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15620,7 +15629,7 @@
         <v>1.25</v>
       </c>
       <c r="AP70">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70">
         <v>1.3</v>
@@ -15748,7 +15757,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16366,7 +16375,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16984,7 +16993,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17190,7 +17199,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17602,7 +17611,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17683,7 +17692,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ80">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR80">
         <v>1.32</v>
@@ -17808,7 +17817,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17889,7 +17898,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18014,7 +18023,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18220,7 +18229,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18632,7 +18641,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18838,7 +18847,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -18916,7 +18925,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ86">
         <v>0.44</v>
@@ -19044,7 +19053,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19250,7 +19259,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19868,7 +19877,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20074,7 +20083,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20280,7 +20289,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q93">
         <v>2.9</v>
@@ -20692,7 +20701,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20773,7 +20782,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ95">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR95">
         <v>1.8</v>
@@ -20898,7 +20907,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -20976,7 +20985,7 @@
         <v>1.4</v>
       </c>
       <c r="AP96">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ96">
         <v>1.11</v>
@@ -21516,7 +21525,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21597,7 +21606,7 @@
         <v>2</v>
       </c>
       <c r="AQ99">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -21928,7 +21937,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22134,7 +22143,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22340,7 +22349,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22752,7 +22761,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23036,7 +23045,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23164,7 +23173,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23782,7 +23791,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23988,7 +23997,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24069,7 +24078,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ111">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR111">
         <v>1.64</v>
@@ -24400,7 +24409,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24687,7 +24696,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ114">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -24812,7 +24821,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -24890,7 +24899,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ115">
         <v>0.25</v>
@@ -25018,7 +25027,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25224,7 +25233,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25636,7 +25645,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26048,7 +26057,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26254,7 +26263,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26460,7 +26469,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26872,7 +26881,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27078,7 +27087,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27284,7 +27293,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27490,7 +27499,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27571,7 +27580,7 @@
         <v>2</v>
       </c>
       <c r="AQ128">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -27774,7 +27783,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ129">
         <v>0.5600000000000001</v>
@@ -27902,7 +27911,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -27980,7 +27989,7 @@
         <v>0.33</v>
       </c>
       <c r="AP130">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ130">
         <v>0.5600000000000001</v>
@@ -28189,7 +28198,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ131">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR131">
         <v>1.61</v>
@@ -28726,7 +28735,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30168,7 +30177,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30786,7 +30795,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -30992,7 +31001,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31198,7 +31207,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31279,7 +31288,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ146">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR146">
         <v>1.41</v>
@@ -31610,7 +31619,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32100,7 +32109,7 @@
         <v>1.29</v>
       </c>
       <c r="AP150">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ150">
         <v>1.33</v>
@@ -32228,7 +32237,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32640,7 +32649,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32721,7 +32730,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ153">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32846,7 +32855,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33258,7 +33267,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33464,7 +33473,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33670,7 +33679,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34082,7 +34091,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34288,7 +34297,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34906,7 +34915,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35112,7 +35121,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35318,7 +35327,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35524,7 +35533,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -36142,7 +36151,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36299,6 +36308,418 @@
       </c>
       <c r="BP170">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7516460</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45670.58333333334</v>
+      </c>
+      <c r="F171">
+        <v>19</v>
+      </c>
+      <c r="G171" t="s">
+        <v>81</v>
+      </c>
+      <c r="H171" t="s">
+        <v>71</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>5</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>5</v>
+      </c>
+      <c r="O171" t="s">
+        <v>212</v>
+      </c>
+      <c r="P171" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q171">
+        <v>2.5</v>
+      </c>
+      <c r="R171">
+        <v>2.15</v>
+      </c>
+      <c r="S171">
+        <v>3.8</v>
+      </c>
+      <c r="T171">
+        <v>1.34</v>
+      </c>
+      <c r="U171">
+        <v>2.95</v>
+      </c>
+      <c r="V171">
+        <v>2.55</v>
+      </c>
+      <c r="W171">
+        <v>1.44</v>
+      </c>
+      <c r="X171">
+        <v>6.25</v>
+      </c>
+      <c r="Y171">
+        <v>1.1</v>
+      </c>
+      <c r="Z171">
+        <v>1.95</v>
+      </c>
+      <c r="AA171">
+        <v>3.66</v>
+      </c>
+      <c r="AB171">
+        <v>3.76</v>
+      </c>
+      <c r="AC171">
+        <v>1.05</v>
+      </c>
+      <c r="AD171">
+        <v>13</v>
+      </c>
+      <c r="AE171">
+        <v>1.25</v>
+      </c>
+      <c r="AF171">
+        <v>3.82</v>
+      </c>
+      <c r="AG171">
+        <v>1.75</v>
+      </c>
+      <c r="AH171">
+        <v>1.95</v>
+      </c>
+      <c r="AI171">
+        <v>1.66</v>
+      </c>
+      <c r="AJ171">
+        <v>2.05</v>
+      </c>
+      <c r="AK171">
+        <v>1.3</v>
+      </c>
+      <c r="AL171">
+        <v>1.3</v>
+      </c>
+      <c r="AM171">
+        <v>1.9</v>
+      </c>
+      <c r="AN171">
+        <v>2.75</v>
+      </c>
+      <c r="AO171">
+        <v>1.75</v>
+      </c>
+      <c r="AP171">
+        <v>2.78</v>
+      </c>
+      <c r="AQ171">
+        <v>1.56</v>
+      </c>
+      <c r="AR171">
+        <v>1.84</v>
+      </c>
+      <c r="AS171">
+        <v>1.3</v>
+      </c>
+      <c r="AT171">
+        <v>3.14</v>
+      </c>
+      <c r="AU171">
+        <v>10</v>
+      </c>
+      <c r="AV171">
+        <v>2</v>
+      </c>
+      <c r="AW171">
+        <v>12</v>
+      </c>
+      <c r="AX171">
+        <v>9</v>
+      </c>
+      <c r="AY171">
+        <v>25</v>
+      </c>
+      <c r="AZ171">
+        <v>13</v>
+      </c>
+      <c r="BA171">
+        <v>8</v>
+      </c>
+      <c r="BB171">
+        <v>3</v>
+      </c>
+      <c r="BC171">
+        <v>11</v>
+      </c>
+      <c r="BD171">
+        <v>1.61</v>
+      </c>
+      <c r="BE171">
+        <v>6.5</v>
+      </c>
+      <c r="BF171">
+        <v>2.55</v>
+      </c>
+      <c r="BG171">
+        <v>1.35</v>
+      </c>
+      <c r="BH171">
+        <v>2.88</v>
+      </c>
+      <c r="BI171">
+        <v>1.6</v>
+      </c>
+      <c r="BJ171">
+        <v>2.17</v>
+      </c>
+      <c r="BK171">
+        <v>1.96</v>
+      </c>
+      <c r="BL171">
+        <v>1.73</v>
+      </c>
+      <c r="BM171">
+        <v>2.5</v>
+      </c>
+      <c r="BN171">
+        <v>1.46</v>
+      </c>
+      <c r="BO171">
+        <v>3.3</v>
+      </c>
+      <c r="BP171">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7516456</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45670.58333333334</v>
+      </c>
+      <c r="F172">
+        <v>19</v>
+      </c>
+      <c r="G172" t="s">
+        <v>79</v>
+      </c>
+      <c r="H172" t="s">
+        <v>73</v>
+      </c>
+      <c r="I172">
+        <v>2</v>
+      </c>
+      <c r="J172">
+        <v>2</v>
+      </c>
+      <c r="K172">
+        <v>4</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>3</v>
+      </c>
+      <c r="N172">
+        <v>5</v>
+      </c>
+      <c r="O172" t="s">
+        <v>213</v>
+      </c>
+      <c r="P172" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q172">
+        <v>5.5</v>
+      </c>
+      <c r="R172">
+        <v>2.3</v>
+      </c>
+      <c r="S172">
+        <v>2</v>
+      </c>
+      <c r="T172">
+        <v>1.33</v>
+      </c>
+      <c r="U172">
+        <v>3</v>
+      </c>
+      <c r="V172">
+        <v>2.5</v>
+      </c>
+      <c r="W172">
+        <v>1.46</v>
+      </c>
+      <c r="X172">
+        <v>6</v>
+      </c>
+      <c r="Y172">
+        <v>1.11</v>
+      </c>
+      <c r="Z172">
+        <v>5.95</v>
+      </c>
+      <c r="AA172">
+        <v>4.56</v>
+      </c>
+      <c r="AB172">
+        <v>1.5</v>
+      </c>
+      <c r="AC172">
+        <v>1.04</v>
+      </c>
+      <c r="AD172">
+        <v>15</v>
+      </c>
+      <c r="AE172">
+        <v>1.22</v>
+      </c>
+      <c r="AF172">
+        <v>4.12</v>
+      </c>
+      <c r="AG172">
+        <v>1.73</v>
+      </c>
+      <c r="AH172">
+        <v>2</v>
+      </c>
+      <c r="AI172">
+        <v>1.85</v>
+      </c>
+      <c r="AJ172">
+        <v>1.83</v>
+      </c>
+      <c r="AK172">
+        <v>2.5</v>
+      </c>
+      <c r="AL172">
+        <v>1.21</v>
+      </c>
+      <c r="AM172">
+        <v>1.13</v>
+      </c>
+      <c r="AN172">
+        <v>1.43</v>
+      </c>
+      <c r="AO172">
+        <v>2</v>
+      </c>
+      <c r="AP172">
+        <v>1.25</v>
+      </c>
+      <c r="AQ172">
+        <v>2.1</v>
+      </c>
+      <c r="AR172">
+        <v>1.36</v>
+      </c>
+      <c r="AS172">
+        <v>1.57</v>
+      </c>
+      <c r="AT172">
+        <v>2.93</v>
+      </c>
+      <c r="AU172">
+        <v>5</v>
+      </c>
+      <c r="AV172">
+        <v>6</v>
+      </c>
+      <c r="AW172">
+        <v>8</v>
+      </c>
+      <c r="AX172">
+        <v>7</v>
+      </c>
+      <c r="AY172">
+        <v>15</v>
+      </c>
+      <c r="AZ172">
+        <v>14</v>
+      </c>
+      <c r="BA172">
+        <v>2</v>
+      </c>
+      <c r="BB172">
+        <v>6</v>
+      </c>
+      <c r="BC172">
+        <v>8</v>
+      </c>
+      <c r="BD172">
+        <v>3.55</v>
+      </c>
+      <c r="BE172">
+        <v>7</v>
+      </c>
+      <c r="BF172">
+        <v>1.35</v>
+      </c>
+      <c r="BG172">
+        <v>1.4</v>
+      </c>
+      <c r="BH172">
+        <v>2.7</v>
+      </c>
+      <c r="BI172">
+        <v>1.66</v>
+      </c>
+      <c r="BJ172">
+        <v>2.07</v>
+      </c>
+      <c r="BK172">
+        <v>2.05</v>
+      </c>
+      <c r="BL172">
+        <v>1.67</v>
+      </c>
+      <c r="BM172">
+        <v>2.6</v>
+      </c>
+      <c r="BN172">
+        <v>1.43</v>
+      </c>
+      <c r="BO172">
+        <v>3.4</v>
+      </c>
+      <c r="BP172">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -36450,22 +36450,22 @@
         <v>3.14</v>
       </c>
       <c r="AU171">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV171">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW171">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AX171">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY171">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ171">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA171">
         <v>8</v>
@@ -36662,16 +36662,16 @@
         <v>6</v>
       </c>
       <c r="AW172">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX172">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY172">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ172">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA172">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,9 @@
     <t>['1', '44']</t>
   </si>
   <si>
+    <t>['21', '90+11']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1287,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1749,7 +1752,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2573,7 +2576,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2779,7 +2782,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2985,7 +2988,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3191,7 +3194,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3397,7 +3400,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3478,7 +3481,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ11">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3603,7 +3606,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3809,7 +3812,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4015,7 +4018,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4096,7 +4099,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4221,7 +4224,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4299,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ15">
         <v>0.78</v>
@@ -4427,7 +4430,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4505,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>0.5600000000000001</v>
@@ -4633,7 +4636,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4711,10 +4714,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ17">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4839,7 +4842,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -4920,7 +4923,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ18">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5123,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ19">
         <v>1.56</v>
@@ -5457,7 +5460,7 @@
         <v>91</v>
       </c>
       <c r="P21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q21">
         <v>2.85</v>
@@ -5663,7 +5666,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5869,7 +5872,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6075,7 +6078,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6281,7 +6284,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6693,7 +6696,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7186,7 +7189,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ29">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR29">
         <v>1.71</v>
@@ -7311,7 +7314,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7392,7 +7395,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ30">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AR30">
         <v>1.28</v>
@@ -7517,7 +7520,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7595,7 +7598,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ31">
         <v>0.5600000000000001</v>
@@ -8007,7 +8010,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>0.88</v>
@@ -8135,7 +8138,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8213,10 +8216,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ34">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR34">
         <v>0.72</v>
@@ -8341,7 +8344,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8547,7 +8550,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8753,7 +8756,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9040,7 +9043,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ38">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR38">
         <v>2.66</v>
@@ -9165,7 +9168,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9371,7 +9374,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9783,7 +9786,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9989,7 +9992,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10195,7 +10198,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10607,7 +10610,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10891,10 +10894,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ47">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR47">
         <v>0.7</v>
@@ -11225,7 +11228,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11306,7 +11309,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ49">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AR49">
         <v>1.64</v>
@@ -11637,7 +11640,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11718,7 +11721,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ51">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR51">
         <v>1.43</v>
@@ -11843,7 +11846,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12049,7 +12052,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12127,7 +12130,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
         <v>1.3</v>
@@ -12539,7 +12542,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ55">
         <v>0.44</v>
@@ -12667,7 +12670,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12873,7 +12876,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13160,7 +13163,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13285,7 +13288,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13491,7 +13494,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13697,7 +13700,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13903,7 +13906,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14109,7 +14112,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14315,7 +14318,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14521,7 +14524,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14808,7 +14811,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ66">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -14933,7 +14936,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15217,7 +15220,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ68">
         <v>0.44</v>
@@ -15345,7 +15348,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15423,7 +15426,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ69">
         <v>1.11</v>
@@ -15551,7 +15554,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15757,7 +15760,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -15838,7 +15841,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ71">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR71">
         <v>1.33</v>
@@ -16247,7 +16250,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ73">
         <v>1.22</v>
@@ -16375,7 +16378,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16993,7 +16996,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17074,7 +17077,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ77">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17199,7 +17202,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17483,7 +17486,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17611,7 +17614,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17817,7 +17820,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18023,7 +18026,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18104,7 +18107,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ82">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR82">
         <v>1.45</v>
@@ -18229,7 +18232,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18513,7 +18516,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ84">
         <v>1.11</v>
@@ -18641,7 +18644,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18722,7 +18725,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ85">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -18847,7 +18850,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19053,7 +19056,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19131,7 +19134,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ87">
         <v>1</v>
@@ -19259,7 +19262,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19546,7 +19549,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ89">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR89">
         <v>1.9</v>
@@ -19749,7 +19752,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ90">
         <v>1.3</v>
@@ -19877,7 +19880,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20083,7 +20086,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20161,7 +20164,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ92">
         <v>0.67</v>
@@ -20289,7 +20292,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q93">
         <v>2.9</v>
@@ -20370,7 +20373,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR93">
         <v>1.31</v>
@@ -20701,7 +20704,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20779,7 +20782,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
         <v>1.56</v>
@@ -20907,7 +20910,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21525,7 +21528,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21937,7 +21940,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22143,7 +22146,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22224,7 +22227,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ102">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR102">
         <v>1.28</v>
@@ -22349,7 +22352,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22427,7 +22430,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ103">
         <v>0.5600000000000001</v>
@@ -22761,7 +22764,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23173,7 +23176,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23254,7 +23257,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ107">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR107">
         <v>1.87</v>
@@ -23663,7 +23666,7 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ109">
         <v>1.22</v>
@@ -23791,7 +23794,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23872,7 +23875,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ110">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR110">
         <v>1.36</v>
@@ -23997,7 +24000,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24281,7 +24284,7 @@
         <v>1.17</v>
       </c>
       <c r="AP112">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ112">
         <v>1.11</v>
@@ -24409,7 +24412,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24490,7 +24493,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ113">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24821,7 +24824,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25027,7 +25030,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25233,7 +25236,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25311,7 +25314,7 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>0.67</v>
@@ -25645,7 +25648,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25932,7 +25935,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ120">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR120">
         <v>1.52</v>
@@ -26057,7 +26060,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26263,7 +26266,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26341,7 +26344,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ122">
         <v>0.67</v>
@@ -26469,7 +26472,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26881,7 +26884,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27087,7 +27090,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27165,7 +27168,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ126">
         <v>1.22</v>
@@ -27293,7 +27296,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27499,7 +27502,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27911,7 +27914,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28195,7 +28198,7 @@
         <v>2.43</v>
       </c>
       <c r="AP131">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
         <v>2.1</v>
@@ -28404,7 +28407,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ132">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28735,7 +28738,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -28816,7 +28819,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ134">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AR134">
         <v>1.23</v>
@@ -29019,7 +29022,7 @@
         <v>0.33</v>
       </c>
       <c r="AP135">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ135">
         <v>0.25</v>
@@ -29225,10 +29228,10 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ136">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -30177,7 +30180,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30255,7 +30258,7 @@
         <v>0.71</v>
       </c>
       <c r="AP141">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ141">
         <v>0.67</v>
@@ -30795,7 +30798,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31001,7 +31004,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31207,7 +31210,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31494,7 +31497,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ147">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR147">
         <v>1.24</v>
@@ -31619,7 +31622,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31697,7 +31700,7 @@
         <v>0.71</v>
       </c>
       <c r="AP148">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ148">
         <v>0.78</v>
@@ -31903,7 +31906,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ149">
         <v>0.5600000000000001</v>
@@ -32112,7 +32115,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ150">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR150">
         <v>1.84</v>
@@ -32237,7 +32240,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32318,7 +32321,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ151">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32524,7 +32527,7 @@
         <v>2</v>
       </c>
       <c r="AQ152">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR152">
         <v>1.63</v>
@@ -32649,7 +32652,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32727,7 +32730,7 @@
         <v>1.86</v>
       </c>
       <c r="AP153">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ153">
         <v>1.56</v>
@@ -32855,7 +32858,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -32933,7 +32936,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ154">
         <v>0.5600000000000001</v>
@@ -33267,7 +33270,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33473,7 +33476,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33679,7 +33682,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34091,7 +34094,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34297,7 +34300,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34915,7 +34918,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -34996,7 +34999,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ164">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR164">
         <v>1.61</v>
@@ -35121,7 +35124,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35199,10 +35202,10 @@
         <v>1.13</v>
       </c>
       <c r="AP165">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ165">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR165">
         <v>1.23</v>
@@ -35327,7 +35330,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35405,10 +35408,10 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR166">
         <v>1.54</v>
@@ -35533,7 +35536,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -36023,7 +36026,7 @@
         <v>0.63</v>
       </c>
       <c r="AP169">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ169">
         <v>0.5600000000000001</v>
@@ -36151,7 +36154,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36229,10 +36232,10 @@
         <v>3</v>
       </c>
       <c r="AP170">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ170">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AR170">
         <v>1.59</v>
@@ -36563,7 +36566,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36719,6 +36722,830 @@
         <v>3.4</v>
       </c>
       <c r="BP172">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7516468</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45674.58333333334</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>87</v>
+      </c>
+      <c r="H173" t="s">
+        <v>70</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>2</v>
+      </c>
+      <c r="O173" t="s">
+        <v>135</v>
+      </c>
+      <c r="P173" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q173">
+        <v>6.25</v>
+      </c>
+      <c r="R173">
+        <v>2.75</v>
+      </c>
+      <c r="S173">
+        <v>1.68</v>
+      </c>
+      <c r="T173">
+        <v>1.21</v>
+      </c>
+      <c r="U173">
+        <v>4</v>
+      </c>
+      <c r="V173">
+        <v>1.95</v>
+      </c>
+      <c r="W173">
+        <v>1.75</v>
+      </c>
+      <c r="X173">
+        <v>4</v>
+      </c>
+      <c r="Y173">
+        <v>1.21</v>
+      </c>
+      <c r="Z173">
+        <v>8.41</v>
+      </c>
+      <c r="AA173">
+        <v>5.98</v>
+      </c>
+      <c r="AB173">
+        <v>1.29</v>
+      </c>
+      <c r="AC173">
+        <v>1.01</v>
+      </c>
+      <c r="AD173">
+        <v>29</v>
+      </c>
+      <c r="AE173">
+        <v>1.08</v>
+      </c>
+      <c r="AF173">
+        <v>7.32</v>
+      </c>
+      <c r="AG173">
+        <v>1.32</v>
+      </c>
+      <c r="AH173">
+        <v>3.25</v>
+      </c>
+      <c r="AI173">
+        <v>1.65</v>
+      </c>
+      <c r="AJ173">
+        <v>2.1</v>
+      </c>
+      <c r="AK173">
+        <v>3.4</v>
+      </c>
+      <c r="AL173">
+        <v>1.13</v>
+      </c>
+      <c r="AM173">
+        <v>1.08</v>
+      </c>
+      <c r="AN173">
+        <v>0.7</v>
+      </c>
+      <c r="AO173">
+        <v>3</v>
+      </c>
+      <c r="AP173">
+        <v>0.73</v>
+      </c>
+      <c r="AQ173">
+        <v>2.78</v>
+      </c>
+      <c r="AR173">
+        <v>1.25</v>
+      </c>
+      <c r="AS173">
+        <v>1.91</v>
+      </c>
+      <c r="AT173">
+        <v>3.16</v>
+      </c>
+      <c r="AU173">
+        <v>4</v>
+      </c>
+      <c r="AV173">
+        <v>8</v>
+      </c>
+      <c r="AW173">
+        <v>4</v>
+      </c>
+      <c r="AX173">
+        <v>17</v>
+      </c>
+      <c r="AY173">
+        <v>9</v>
+      </c>
+      <c r="AZ173">
+        <v>32</v>
+      </c>
+      <c r="BA173">
+        <v>5</v>
+      </c>
+      <c r="BB173">
+        <v>9</v>
+      </c>
+      <c r="BC173">
+        <v>14</v>
+      </c>
+      <c r="BD173">
+        <v>4.4</v>
+      </c>
+      <c r="BE173">
+        <v>8.5</v>
+      </c>
+      <c r="BF173">
+        <v>1.23</v>
+      </c>
+      <c r="BG173">
+        <v>1.21</v>
+      </c>
+      <c r="BH173">
+        <v>3.8</v>
+      </c>
+      <c r="BI173">
+        <v>1.37</v>
+      </c>
+      <c r="BJ173">
+        <v>2.8</v>
+      </c>
+      <c r="BK173">
+        <v>1.6</v>
+      </c>
+      <c r="BL173">
+        <v>2.17</v>
+      </c>
+      <c r="BM173">
+        <v>1.95</v>
+      </c>
+      <c r="BN173">
+        <v>1.75</v>
+      </c>
+      <c r="BO173">
+        <v>2.4</v>
+      </c>
+      <c r="BP173">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7516463</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45675.3125</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>83</v>
+      </c>
+      <c r="H174" t="s">
+        <v>77</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>2</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>2</v>
+      </c>
+      <c r="O174" t="s">
+        <v>214</v>
+      </c>
+      <c r="P174" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q174">
+        <v>2.7</v>
+      </c>
+      <c r="R174">
+        <v>2.15</v>
+      </c>
+      <c r="S174">
+        <v>3.5</v>
+      </c>
+      <c r="T174">
+        <v>1.36</v>
+      </c>
+      <c r="U174">
+        <v>2.9</v>
+      </c>
+      <c r="V174">
+        <v>2.65</v>
+      </c>
+      <c r="W174">
+        <v>1.42</v>
+      </c>
+      <c r="X174">
+        <v>6.5</v>
+      </c>
+      <c r="Y174">
+        <v>1.09</v>
+      </c>
+      <c r="Z174">
+        <v>2.17</v>
+      </c>
+      <c r="AA174">
+        <v>3.56</v>
+      </c>
+      <c r="AB174">
+        <v>3.23</v>
+      </c>
+      <c r="AC174">
+        <v>1.03</v>
+      </c>
+      <c r="AD174">
+        <v>10.65</v>
+      </c>
+      <c r="AE174">
+        <v>1.27</v>
+      </c>
+      <c r="AF174">
+        <v>3.61</v>
+      </c>
+      <c r="AG174">
+        <v>1.88</v>
+      </c>
+      <c r="AH174">
+        <v>1.96</v>
+      </c>
+      <c r="AI174">
+        <v>1.68</v>
+      </c>
+      <c r="AJ174">
+        <v>2</v>
+      </c>
+      <c r="AK174">
+        <v>1.35</v>
+      </c>
+      <c r="AL174">
+        <v>1.28</v>
+      </c>
+      <c r="AM174">
+        <v>1.65</v>
+      </c>
+      <c r="AN174">
+        <v>1.78</v>
+      </c>
+      <c r="AO174">
+        <v>1.33</v>
+      </c>
+      <c r="AP174">
+        <v>1.9</v>
+      </c>
+      <c r="AQ174">
+        <v>1.2</v>
+      </c>
+      <c r="AR174">
+        <v>1.54</v>
+      </c>
+      <c r="AS174">
+        <v>1.17</v>
+      </c>
+      <c r="AT174">
+        <v>2.71</v>
+      </c>
+      <c r="AU174">
+        <v>5</v>
+      </c>
+      <c r="AV174">
+        <v>3</v>
+      </c>
+      <c r="AW174">
+        <v>3</v>
+      </c>
+      <c r="AX174">
+        <v>8</v>
+      </c>
+      <c r="AY174">
+        <v>10</v>
+      </c>
+      <c r="AZ174">
+        <v>13</v>
+      </c>
+      <c r="BA174">
+        <v>2</v>
+      </c>
+      <c r="BB174">
+        <v>8</v>
+      </c>
+      <c r="BC174">
+        <v>10</v>
+      </c>
+      <c r="BD174">
+        <v>1.92</v>
+      </c>
+      <c r="BE174">
+        <v>6.4</v>
+      </c>
+      <c r="BF174">
+        <v>2.07</v>
+      </c>
+      <c r="BG174">
+        <v>1.37</v>
+      </c>
+      <c r="BH174">
+        <v>2.8</v>
+      </c>
+      <c r="BI174">
+        <v>1.64</v>
+      </c>
+      <c r="BJ174">
+        <v>2.1</v>
+      </c>
+      <c r="BK174">
+        <v>2</v>
+      </c>
+      <c r="BL174">
+        <v>1.7</v>
+      </c>
+      <c r="BM174">
+        <v>2.55</v>
+      </c>
+      <c r="BN174">
+        <v>1.44</v>
+      </c>
+      <c r="BO174">
+        <v>3.4</v>
+      </c>
+      <c r="BP174">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7516462</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45675.41666666666</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>85</v>
+      </c>
+      <c r="H175" t="s">
+        <v>78</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="O175" t="s">
+        <v>91</v>
+      </c>
+      <c r="P175" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q175">
+        <v>2.6</v>
+      </c>
+      <c r="R175">
+        <v>2.1</v>
+      </c>
+      <c r="S175">
+        <v>3.9</v>
+      </c>
+      <c r="T175">
+        <v>1.38</v>
+      </c>
+      <c r="U175">
+        <v>2.75</v>
+      </c>
+      <c r="V175">
+        <v>2.75</v>
+      </c>
+      <c r="W175">
+        <v>1.39</v>
+      </c>
+      <c r="X175">
+        <v>7</v>
+      </c>
+      <c r="Y175">
+        <v>1.08</v>
+      </c>
+      <c r="Z175">
+        <v>2.13</v>
+      </c>
+      <c r="AA175">
+        <v>3.27</v>
+      </c>
+      <c r="AB175">
+        <v>3.46</v>
+      </c>
+      <c r="AC175">
+        <v>1.05</v>
+      </c>
+      <c r="AD175">
+        <v>9</v>
+      </c>
+      <c r="AE175">
+        <v>1.29</v>
+      </c>
+      <c r="AF175">
+        <v>3.44</v>
+      </c>
+      <c r="AG175">
+        <v>1.93</v>
+      </c>
+      <c r="AH175">
+        <v>1.83</v>
+      </c>
+      <c r="AI175">
+        <v>1.75</v>
+      </c>
+      <c r="AJ175">
+        <v>1.93</v>
+      </c>
+      <c r="AK175">
+        <v>1.28</v>
+      </c>
+      <c r="AL175">
+        <v>1.3</v>
+      </c>
+      <c r="AM175">
+        <v>1.75</v>
+      </c>
+      <c r="AN175">
+        <v>2.22</v>
+      </c>
+      <c r="AO175">
+        <v>0.44</v>
+      </c>
+      <c r="AP175">
+        <v>2.1</v>
+      </c>
+      <c r="AQ175">
+        <v>0.5</v>
+      </c>
+      <c r="AR175">
+        <v>1.46</v>
+      </c>
+      <c r="AS175">
+        <v>1.15</v>
+      </c>
+      <c r="AT175">
+        <v>2.61</v>
+      </c>
+      <c r="AU175">
+        <v>4</v>
+      </c>
+      <c r="AV175">
+        <v>5</v>
+      </c>
+      <c r="AW175">
+        <v>9</v>
+      </c>
+      <c r="AX175">
+        <v>6</v>
+      </c>
+      <c r="AY175">
+        <v>14</v>
+      </c>
+      <c r="AZ175">
+        <v>12</v>
+      </c>
+      <c r="BA175">
+        <v>5</v>
+      </c>
+      <c r="BB175">
+        <v>7</v>
+      </c>
+      <c r="BC175">
+        <v>12</v>
+      </c>
+      <c r="BD175">
+        <v>1.68</v>
+      </c>
+      <c r="BE175">
+        <v>6.4</v>
+      </c>
+      <c r="BF175">
+        <v>2.43</v>
+      </c>
+      <c r="BG175">
+        <v>1.37</v>
+      </c>
+      <c r="BH175">
+        <v>2.8</v>
+      </c>
+      <c r="BI175">
+        <v>1.64</v>
+      </c>
+      <c r="BJ175">
+        <v>2.1</v>
+      </c>
+      <c r="BK175">
+        <v>2.02</v>
+      </c>
+      <c r="BL175">
+        <v>1.68</v>
+      </c>
+      <c r="BM175">
+        <v>2.55</v>
+      </c>
+      <c r="BN175">
+        <v>1.44</v>
+      </c>
+      <c r="BO175">
+        <v>3.4</v>
+      </c>
+      <c r="BP175">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7516469</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45675.54166666666</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>84</v>
+      </c>
+      <c r="H176" t="s">
+        <v>76</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="O176" t="s">
+        <v>91</v>
+      </c>
+      <c r="P176" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q176">
+        <v>2.55</v>
+      </c>
+      <c r="R176">
+        <v>2.2</v>
+      </c>
+      <c r="S176">
+        <v>3.6</v>
+      </c>
+      <c r="T176">
+        <v>1.33</v>
+      </c>
+      <c r="U176">
+        <v>3</v>
+      </c>
+      <c r="V176">
+        <v>2.5</v>
+      </c>
+      <c r="W176">
+        <v>1.46</v>
+      </c>
+      <c r="X176">
+        <v>6</v>
+      </c>
+      <c r="Y176">
+        <v>1.11</v>
+      </c>
+      <c r="Z176">
+        <v>2.07</v>
+      </c>
+      <c r="AA176">
+        <v>3.57</v>
+      </c>
+      <c r="AB176">
+        <v>3.33</v>
+      </c>
+      <c r="AC176">
+        <v>1.05</v>
+      </c>
+      <c r="AD176">
+        <v>13</v>
+      </c>
+      <c r="AE176">
+        <v>1.22</v>
+      </c>
+      <c r="AF176">
+        <v>4.12</v>
+      </c>
+      <c r="AG176">
+        <v>1.75</v>
+      </c>
+      <c r="AH176">
+        <v>2.03</v>
+      </c>
+      <c r="AI176">
+        <v>1.63</v>
+      </c>
+      <c r="AJ176">
+        <v>2.1</v>
+      </c>
+      <c r="AK176">
+        <v>1.31</v>
+      </c>
+      <c r="AL176">
+        <v>1.27</v>
+      </c>
+      <c r="AM176">
+        <v>1.73</v>
+      </c>
+      <c r="AN176">
+        <v>2.11</v>
+      </c>
+      <c r="AO176">
+        <v>2.11</v>
+      </c>
+      <c r="AP176">
+        <v>2</v>
+      </c>
+      <c r="AQ176">
+        <v>2</v>
+      </c>
+      <c r="AR176">
+        <v>1.49</v>
+      </c>
+      <c r="AS176">
+        <v>1.25</v>
+      </c>
+      <c r="AT176">
+        <v>2.74</v>
+      </c>
+      <c r="AU176">
+        <v>5</v>
+      </c>
+      <c r="AV176">
+        <v>4</v>
+      </c>
+      <c r="AW176">
+        <v>20</v>
+      </c>
+      <c r="AX176">
+        <v>2</v>
+      </c>
+      <c r="AY176">
+        <v>35</v>
+      </c>
+      <c r="AZ176">
+        <v>6</v>
+      </c>
+      <c r="BA176">
+        <v>5</v>
+      </c>
+      <c r="BB176">
+        <v>4</v>
+      </c>
+      <c r="BC176">
+        <v>9</v>
+      </c>
+      <c r="BD176">
+        <v>1.74</v>
+      </c>
+      <c r="BE176">
+        <v>6.4</v>
+      </c>
+      <c r="BF176">
+        <v>2.33</v>
+      </c>
+      <c r="BG176">
+        <v>1.37</v>
+      </c>
+      <c r="BH176">
+        <v>2.8</v>
+      </c>
+      <c r="BI176">
+        <v>1.65</v>
+      </c>
+      <c r="BJ176">
+        <v>2.08</v>
+      </c>
+      <c r="BK176">
+        <v>2.05</v>
+      </c>
+      <c r="BL176">
+        <v>1.67</v>
+      </c>
+      <c r="BM176">
+        <v>2.63</v>
+      </c>
+      <c r="BN176">
+        <v>1.41</v>
+      </c>
+      <c r="BO176">
+        <v>3.4</v>
+      </c>
+      <c r="BP176">
         <v>1.26</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="309">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,15 @@
     <t>['21', '90+11']</t>
   </si>
   <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['20', '63', '82']</t>
+  </si>
+  <si>
+    <t>['45+2', '65', '75']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -698,9 +707,6 @@
   </si>
   <si>
     <t>['30']</t>
-  </si>
-  <si>
-    <t>['8']</t>
   </si>
   <si>
     <t>['45+4']</t>
@@ -929,6 +935,12 @@
   </si>
   <si>
     <t>['14', '25', '60']</t>
+  </si>
+  <si>
+    <t>['53', '70', '87']</t>
+  </si>
+  <si>
+    <t>['69', '71', '74', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP176"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1752,7 +1764,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2576,7 +2588,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2782,7 +2794,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2988,7 +3000,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3194,7 +3206,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3400,7 +3412,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3478,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ11">
         <v>2.78</v>
@@ -3606,7 +3618,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3812,7 +3824,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -3890,10 +3902,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ13">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4018,7 +4030,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4096,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ14">
         <v>1.2</v>
@@ -4224,7 +4236,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4305,7 +4317,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ15">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4430,7 +4442,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4511,7 +4523,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4636,7 +4648,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4842,7 +4854,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -4920,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ18">
         <v>0.5</v>
@@ -5129,7 +5141,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ19">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5460,7 +5472,7 @@
         <v>91</v>
       </c>
       <c r="P21" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="Q21">
         <v>2.85</v>
@@ -5666,7 +5678,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5872,7 +5884,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6078,7 +6090,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6284,7 +6296,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6365,7 +6377,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR25">
         <v>1.86</v>
@@ -6571,7 +6583,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ26">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR26">
         <v>1.44</v>
@@ -6696,7 +6708,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6777,7 +6789,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ27">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -6980,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ28">
         <v>1.11</v>
@@ -7186,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ29">
         <v>0.5</v>
@@ -7314,7 +7326,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7392,7 +7404,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ30">
         <v>2.78</v>
@@ -7520,7 +7532,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7601,7 +7613,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ31">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>1.45</v>
@@ -7804,7 +7816,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ32">
         <v>0.44</v>
@@ -8138,7 +8150,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8344,7 +8356,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8550,7 +8562,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8756,7 +8768,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9168,7 +9180,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9249,7 +9261,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ39">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR39">
         <v>1.4</v>
@@ -9374,7 +9386,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9786,7 +9798,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9992,7 +10004,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10198,7 +10210,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10610,7 +10622,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11100,7 +11112,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ48">
         <v>0.88</v>
@@ -11228,7 +11240,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11515,7 +11527,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ50">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR50">
         <v>1.45</v>
@@ -11640,7 +11652,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11846,7 +11858,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11924,10 +11936,10 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ52">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR52">
         <v>1.43</v>
@@ -12052,7 +12064,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12336,7 +12348,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ54">
         <v>1.11</v>
@@ -12670,7 +12682,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12876,7 +12888,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13288,7 +13300,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13369,7 +13381,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ59">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>2.34</v>
@@ -13494,7 +13506,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13572,7 +13584,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ60">
         <v>0.5600000000000001</v>
@@ -13700,7 +13712,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13906,7 +13918,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14112,7 +14124,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14193,7 +14205,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ63">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -14318,7 +14330,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14524,7 +14536,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14605,7 +14617,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14936,7 +14948,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15014,7 +15026,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ67">
         <v>0.88</v>
@@ -15348,7 +15360,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15554,7 +15566,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15632,7 +15644,7 @@
         <v>1.25</v>
       </c>
       <c r="AP70">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ70">
         <v>1.3</v>
@@ -15760,7 +15772,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -15838,7 +15850,7 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ71">
         <v>2</v>
@@ -16047,7 +16059,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ72">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16378,7 +16390,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16868,7 +16880,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ76">
         <v>0.67</v>
@@ -16996,7 +17008,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17202,7 +17214,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17614,7 +17626,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17695,7 +17707,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ80">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.32</v>
@@ -17820,7 +17832,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17901,7 +17913,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ81">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18026,7 +18038,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18232,7 +18244,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18310,7 +18322,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ83">
         <v>0.88</v>
@@ -18644,7 +18656,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18850,7 +18862,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -18928,7 +18940,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ86">
         <v>0.44</v>
@@ -19056,7 +19068,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19262,7 +19274,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19343,7 +19355,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ88">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19880,7 +19892,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20086,7 +20098,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20292,7 +20304,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>2.9</v>
@@ -20704,7 +20716,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20785,7 +20797,7 @@
         <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR95">
         <v>1.8</v>
@@ -20910,7 +20922,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -20988,7 +21000,7 @@
         <v>1.4</v>
       </c>
       <c r="AP96">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ96">
         <v>1.11</v>
@@ -21194,7 +21206,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ97">
         <v>0.25</v>
@@ -21403,7 +21415,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ98">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21528,7 +21540,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21609,7 +21621,7 @@
         <v>2</v>
       </c>
       <c r="AQ99">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -21815,7 +21827,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ100">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR100">
         <v>1.54</v>
@@ -21940,7 +21952,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22146,7 +22158,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22352,7 +22364,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22764,7 +22776,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22842,7 +22854,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ105">
         <v>1.3</v>
@@ -23048,7 +23060,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23176,7 +23188,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23794,7 +23806,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23872,7 +23884,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ110">
         <v>1.2</v>
@@ -24000,7 +24012,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24081,7 +24093,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ111">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR111">
         <v>1.64</v>
@@ -24412,7 +24424,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24699,7 +24711,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ114">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -24824,7 +24836,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -24902,7 +24914,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ115">
         <v>0.25</v>
@@ -25030,7 +25042,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25111,7 +25123,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ116">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR116">
         <v>1.6</v>
@@ -25236,7 +25248,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25648,7 +25660,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26060,7 +26072,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26138,7 +26150,7 @@
         <v>0.86</v>
       </c>
       <c r="AP121">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26266,7 +26278,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26472,7 +26484,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26884,7 +26896,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27090,7 +27102,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27296,7 +27308,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27502,7 +27514,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27583,7 +27595,7 @@
         <v>2</v>
       </c>
       <c r="AQ128">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -27786,10 +27798,10 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ129">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -27914,7 +27926,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -27992,7 +28004,7 @@
         <v>0.33</v>
       </c>
       <c r="AP130">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ130">
         <v>0.5600000000000001</v>
@@ -28201,7 +28213,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR131">
         <v>1.61</v>
@@ -28404,7 +28416,7 @@
         <v>2.5</v>
       </c>
       <c r="AP132">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ132">
         <v>2</v>
@@ -28613,7 +28625,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ133">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR133">
         <v>1.67</v>
@@ -28738,7 +28750,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30180,7 +30192,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30798,7 +30810,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -30876,7 +30888,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ144">
         <v>1.22</v>
@@ -31004,7 +31016,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31210,7 +31222,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31288,10 +31300,10 @@
         <v>2.13</v>
       </c>
       <c r="AP146">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ146">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR146">
         <v>1.41</v>
@@ -31622,7 +31634,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31703,7 +31715,7 @@
         <v>2</v>
       </c>
       <c r="AQ148">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR148">
         <v>1.58</v>
@@ -31909,7 +31921,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ149">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR149">
         <v>1.44</v>
@@ -32112,7 +32124,7 @@
         <v>1.29</v>
       </c>
       <c r="AP150">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ150">
         <v>1.2</v>
@@ -32240,7 +32252,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32652,7 +32664,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32733,7 +32745,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ153">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32858,7 +32870,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33270,7 +33282,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33476,7 +33488,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33554,7 +33566,7 @@
         <v>0.88</v>
       </c>
       <c r="AP157">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ157">
         <v>1.11</v>
@@ -33682,7 +33694,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34094,7 +34106,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34300,7 +34312,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34918,7 +34930,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35124,7 +35136,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35330,7 +35342,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35536,7 +35548,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -35617,7 +35629,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ167">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR167">
         <v>1.22</v>
@@ -35823,7 +35835,7 @@
         <v>2</v>
       </c>
       <c r="AQ168">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR168">
         <v>1.65</v>
@@ -36154,7 +36166,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36438,10 +36450,10 @@
         <v>1.75</v>
       </c>
       <c r="AP171">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ171">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR171">
         <v>1.84</v>
@@ -36566,7 +36578,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36644,10 +36656,10 @@
         <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ172">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR172">
         <v>1.36</v>
@@ -36772,7 +36784,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -37547,6 +37559,830 @@
       </c>
       <c r="BP176">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7516461</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45676.3125</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>81</v>
+      </c>
+      <c r="H177" t="s">
+        <v>72</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>1</v>
+      </c>
+      <c r="O177" t="s">
+        <v>215</v>
+      </c>
+      <c r="P177" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q177">
+        <v>2.1</v>
+      </c>
+      <c r="R177">
+        <v>2.2</v>
+      </c>
+      <c r="S177">
+        <v>5</v>
+      </c>
+      <c r="T177">
+        <v>1.34</v>
+      </c>
+      <c r="U177">
+        <v>3</v>
+      </c>
+      <c r="V177">
+        <v>2.5</v>
+      </c>
+      <c r="W177">
+        <v>1.46</v>
+      </c>
+      <c r="X177">
+        <v>6</v>
+      </c>
+      <c r="Y177">
+        <v>1.11</v>
+      </c>
+      <c r="Z177">
+        <v>1.59</v>
+      </c>
+      <c r="AA177">
+        <v>4.11</v>
+      </c>
+      <c r="AB177">
+        <v>5.17</v>
+      </c>
+      <c r="AC177">
+        <v>1.05</v>
+      </c>
+      <c r="AD177">
+        <v>13</v>
+      </c>
+      <c r="AE177">
+        <v>1.22</v>
+      </c>
+      <c r="AF177">
+        <v>4.12</v>
+      </c>
+      <c r="AG177">
+        <v>1.75</v>
+      </c>
+      <c r="AH177">
+        <v>2.03</v>
+      </c>
+      <c r="AI177">
+        <v>1.8</v>
+      </c>
+      <c r="AJ177">
+        <v>1.9</v>
+      </c>
+      <c r="AK177">
+        <v>1.13</v>
+      </c>
+      <c r="AL177">
+        <v>1.2</v>
+      </c>
+      <c r="AM177">
+        <v>2.3</v>
+      </c>
+      <c r="AN177">
+        <v>2.78</v>
+      </c>
+      <c r="AO177">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP177">
+        <v>2.8</v>
+      </c>
+      <c r="AQ177">
+        <v>0.5</v>
+      </c>
+      <c r="AR177">
+        <v>1.85</v>
+      </c>
+      <c r="AS177">
+        <v>1.03</v>
+      </c>
+      <c r="AT177">
+        <v>2.88</v>
+      </c>
+      <c r="AU177">
+        <v>4</v>
+      </c>
+      <c r="AV177">
+        <v>3</v>
+      </c>
+      <c r="AW177">
+        <v>14</v>
+      </c>
+      <c r="AX177">
+        <v>4</v>
+      </c>
+      <c r="AY177">
+        <v>20</v>
+      </c>
+      <c r="AZ177">
+        <v>7</v>
+      </c>
+      <c r="BA177">
+        <v>5</v>
+      </c>
+      <c r="BB177">
+        <v>4</v>
+      </c>
+      <c r="BC177">
+        <v>9</v>
+      </c>
+      <c r="BD177">
+        <v>1.49</v>
+      </c>
+      <c r="BE177">
+        <v>6.5</v>
+      </c>
+      <c r="BF177">
+        <v>2.9</v>
+      </c>
+      <c r="BG177">
+        <v>1.38</v>
+      </c>
+      <c r="BH177">
+        <v>2.7</v>
+      </c>
+      <c r="BI177">
+        <v>1.66</v>
+      </c>
+      <c r="BJ177">
+        <v>2.07</v>
+      </c>
+      <c r="BK177">
+        <v>2.05</v>
+      </c>
+      <c r="BL177">
+        <v>1.66</v>
+      </c>
+      <c r="BM177">
+        <v>2.65</v>
+      </c>
+      <c r="BN177">
+        <v>1.41</v>
+      </c>
+      <c r="BO177">
+        <v>3.45</v>
+      </c>
+      <c r="BP177">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7516466</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45676.41666666666</v>
+      </c>
+      <c r="F178">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>79</v>
+      </c>
+      <c r="H178" t="s">
+        <v>71</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>3</v>
+      </c>
+      <c r="M178">
+        <v>3</v>
+      </c>
+      <c r="N178">
+        <v>6</v>
+      </c>
+      <c r="O178" t="s">
+        <v>216</v>
+      </c>
+      <c r="P178" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q178">
+        <v>2.75</v>
+      </c>
+      <c r="R178">
+        <v>2.1</v>
+      </c>
+      <c r="S178">
+        <v>3.5</v>
+      </c>
+      <c r="T178">
+        <v>1.37</v>
+      </c>
+      <c r="U178">
+        <v>2.8</v>
+      </c>
+      <c r="V178">
+        <v>2.65</v>
+      </c>
+      <c r="W178">
+        <v>1.41</v>
+      </c>
+      <c r="X178">
+        <v>6.75</v>
+      </c>
+      <c r="Y178">
+        <v>1.09</v>
+      </c>
+      <c r="Z178">
+        <v>2.16</v>
+      </c>
+      <c r="AA178">
+        <v>3.42</v>
+      </c>
+      <c r="AB178">
+        <v>3.24</v>
+      </c>
+      <c r="AC178">
+        <v>1.04</v>
+      </c>
+      <c r="AD178">
+        <v>10.06</v>
+      </c>
+      <c r="AE178">
+        <v>1.29</v>
+      </c>
+      <c r="AF178">
+        <v>3.44</v>
+      </c>
+      <c r="AG178">
+        <v>1.88</v>
+      </c>
+      <c r="AH178">
+        <v>1.88</v>
+      </c>
+      <c r="AI178">
+        <v>1.71</v>
+      </c>
+      <c r="AJ178">
+        <v>2</v>
+      </c>
+      <c r="AK178">
+        <v>1.35</v>
+      </c>
+      <c r="AL178">
+        <v>1.25</v>
+      </c>
+      <c r="AM178">
+        <v>1.62</v>
+      </c>
+      <c r="AN178">
+        <v>1.25</v>
+      </c>
+      <c r="AO178">
+        <v>1.56</v>
+      </c>
+      <c r="AP178">
+        <v>1.22</v>
+      </c>
+      <c r="AQ178">
+        <v>1.5</v>
+      </c>
+      <c r="AR178">
+        <v>1.34</v>
+      </c>
+      <c r="AS178">
+        <v>1.24</v>
+      </c>
+      <c r="AT178">
+        <v>2.58</v>
+      </c>
+      <c r="AU178">
+        <v>8</v>
+      </c>
+      <c r="AV178">
+        <v>5</v>
+      </c>
+      <c r="AW178">
+        <v>6</v>
+      </c>
+      <c r="AX178">
+        <v>10</v>
+      </c>
+      <c r="AY178">
+        <v>16</v>
+      </c>
+      <c r="AZ178">
+        <v>17</v>
+      </c>
+      <c r="BA178">
+        <v>12</v>
+      </c>
+      <c r="BB178">
+        <v>7</v>
+      </c>
+      <c r="BC178">
+        <v>19</v>
+      </c>
+      <c r="BD178">
+        <v>1.74</v>
+      </c>
+      <c r="BE178">
+        <v>6.5</v>
+      </c>
+      <c r="BF178">
+        <v>2.32</v>
+      </c>
+      <c r="BG178">
+        <v>1.34</v>
+      </c>
+      <c r="BH178">
+        <v>2.9</v>
+      </c>
+      <c r="BI178">
+        <v>1.58</v>
+      </c>
+      <c r="BJ178">
+        <v>2.18</v>
+      </c>
+      <c r="BK178">
+        <v>1.95</v>
+      </c>
+      <c r="BL178">
+        <v>1.74</v>
+      </c>
+      <c r="BM178">
+        <v>2.48</v>
+      </c>
+      <c r="BN178">
+        <v>1.47</v>
+      </c>
+      <c r="BO178">
+        <v>3.2</v>
+      </c>
+      <c r="BP178">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7516464</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45676.54166666666</v>
+      </c>
+      <c r="F179">
+        <v>20</v>
+      </c>
+      <c r="G179" t="s">
+        <v>86</v>
+      </c>
+      <c r="H179" t="s">
+        <v>75</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179">
+        <v>3</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>3</v>
+      </c>
+      <c r="O179" t="s">
+        <v>217</v>
+      </c>
+      <c r="P179" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q179">
+        <v>2.85</v>
+      </c>
+      <c r="R179">
+        <v>2.1</v>
+      </c>
+      <c r="S179">
+        <v>4</v>
+      </c>
+      <c r="T179">
+        <v>1.45</v>
+      </c>
+      <c r="U179">
+        <v>2.95</v>
+      </c>
+      <c r="V179">
+        <v>2.95</v>
+      </c>
+      <c r="W179">
+        <v>1.45</v>
+      </c>
+      <c r="X179">
+        <v>8</v>
+      </c>
+      <c r="Y179">
+        <v>1.11</v>
+      </c>
+      <c r="Z179">
+        <v>2.12</v>
+      </c>
+      <c r="AA179">
+        <v>3.34</v>
+      </c>
+      <c r="AB179">
+        <v>3.43</v>
+      </c>
+      <c r="AC179">
+        <v>1.04</v>
+      </c>
+      <c r="AD179">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE179">
+        <v>1.27</v>
+      </c>
+      <c r="AF179">
+        <v>3.61</v>
+      </c>
+      <c r="AG179">
+        <v>1.88</v>
+      </c>
+      <c r="AH179">
+        <v>1.88</v>
+      </c>
+      <c r="AI179">
+        <v>1.72</v>
+      </c>
+      <c r="AJ179">
+        <v>2.1</v>
+      </c>
+      <c r="AK179">
+        <v>1.33</v>
+      </c>
+      <c r="AL179">
+        <v>1.36</v>
+      </c>
+      <c r="AM179">
+        <v>1.75</v>
+      </c>
+      <c r="AN179">
+        <v>2.13</v>
+      </c>
+      <c r="AO179">
+        <v>0.78</v>
+      </c>
+      <c r="AP179">
+        <v>2.22</v>
+      </c>
+      <c r="AQ179">
+        <v>0.7</v>
+      </c>
+      <c r="AR179">
+        <v>1.37</v>
+      </c>
+      <c r="AS179">
+        <v>1.09</v>
+      </c>
+      <c r="AT179">
+        <v>2.46</v>
+      </c>
+      <c r="AU179">
+        <v>10</v>
+      </c>
+      <c r="AV179">
+        <v>2</v>
+      </c>
+      <c r="AW179">
+        <v>8</v>
+      </c>
+      <c r="AX179">
+        <v>12</v>
+      </c>
+      <c r="AY179">
+        <v>18</v>
+      </c>
+      <c r="AZ179">
+        <v>14</v>
+      </c>
+      <c r="BA179">
+        <v>11</v>
+      </c>
+      <c r="BB179">
+        <v>5</v>
+      </c>
+      <c r="BC179">
+        <v>16</v>
+      </c>
+      <c r="BD179">
+        <v>1.7</v>
+      </c>
+      <c r="BE179">
+        <v>6.4</v>
+      </c>
+      <c r="BF179">
+        <v>2.4</v>
+      </c>
+      <c r="BG179">
+        <v>1.41</v>
+      </c>
+      <c r="BH179">
+        <v>2.65</v>
+      </c>
+      <c r="BI179">
+        <v>1.68</v>
+      </c>
+      <c r="BJ179">
+        <v>2.04</v>
+      </c>
+      <c r="BK179">
+        <v>2.07</v>
+      </c>
+      <c r="BL179">
+        <v>1.65</v>
+      </c>
+      <c r="BM179">
+        <v>2.65</v>
+      </c>
+      <c r="BN179">
+        <v>1.41</v>
+      </c>
+      <c r="BO179">
+        <v>3.45</v>
+      </c>
+      <c r="BP179">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7516467</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45676.54166666666</v>
+      </c>
+      <c r="F180">
+        <v>20</v>
+      </c>
+      <c r="G180" t="s">
+        <v>82</v>
+      </c>
+      <c r="H180" t="s">
+        <v>73</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>4</v>
+      </c>
+      <c r="N180">
+        <v>4</v>
+      </c>
+      <c r="O180" t="s">
+        <v>91</v>
+      </c>
+      <c r="P180" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q180">
+        <v>9.25</v>
+      </c>
+      <c r="R180">
+        <v>3</v>
+      </c>
+      <c r="S180">
+        <v>1.49</v>
+      </c>
+      <c r="T180">
+        <v>1.19</v>
+      </c>
+      <c r="U180">
+        <v>4.2</v>
+      </c>
+      <c r="V180">
+        <v>1.85</v>
+      </c>
+      <c r="W180">
+        <v>1.83</v>
+      </c>
+      <c r="X180">
+        <v>3.7</v>
+      </c>
+      <c r="Y180">
+        <v>1.24</v>
+      </c>
+      <c r="Z180">
+        <v>16.52</v>
+      </c>
+      <c r="AA180">
+        <v>9.18</v>
+      </c>
+      <c r="AB180">
+        <v>1.12</v>
+      </c>
+      <c r="AC180">
+        <v>1.01</v>
+      </c>
+      <c r="AD180">
+        <v>29</v>
+      </c>
+      <c r="AE180">
+        <v>1.07</v>
+      </c>
+      <c r="AF180">
+        <v>7.76</v>
+      </c>
+      <c r="AG180">
+        <v>1.31</v>
+      </c>
+      <c r="AH180">
+        <v>3.33</v>
+      </c>
+      <c r="AI180">
+        <v>1.9</v>
+      </c>
+      <c r="AJ180">
+        <v>1.78</v>
+      </c>
+      <c r="AK180">
+        <v>5</v>
+      </c>
+      <c r="AL180">
+        <v>1.07</v>
+      </c>
+      <c r="AM180">
+        <v>1.02</v>
+      </c>
+      <c r="AN180">
+        <v>0.33</v>
+      </c>
+      <c r="AO180">
+        <v>2.1</v>
+      </c>
+      <c r="AP180">
+        <v>0.3</v>
+      </c>
+      <c r="AQ180">
+        <v>2.18</v>
+      </c>
+      <c r="AR180">
+        <v>1.28</v>
+      </c>
+      <c r="AS180">
+        <v>1.56</v>
+      </c>
+      <c r="AT180">
+        <v>2.84</v>
+      </c>
+      <c r="AU180">
+        <v>3</v>
+      </c>
+      <c r="AV180">
+        <v>13</v>
+      </c>
+      <c r="AW180">
+        <v>1</v>
+      </c>
+      <c r="AX180">
+        <v>11</v>
+      </c>
+      <c r="AY180">
+        <v>4</v>
+      </c>
+      <c r="AZ180">
+        <v>24</v>
+      </c>
+      <c r="BA180">
+        <v>2</v>
+      </c>
+      <c r="BB180">
+        <v>11</v>
+      </c>
+      <c r="BC180">
+        <v>13</v>
+      </c>
+      <c r="BD180">
+        <v>5.1</v>
+      </c>
+      <c r="BE180">
+        <v>9.5</v>
+      </c>
+      <c r="BF180">
+        <v>1.18</v>
+      </c>
+      <c r="BG180">
+        <v>1.29</v>
+      </c>
+      <c r="BH180">
+        <v>3.2</v>
+      </c>
+      <c r="BI180">
+        <v>1.49</v>
+      </c>
+      <c r="BJ180">
+        <v>2.4</v>
+      </c>
+      <c r="BK180">
+        <v>1.79</v>
+      </c>
+      <c r="BL180">
+        <v>1.9</v>
+      </c>
+      <c r="BM180">
+        <v>2.23</v>
+      </c>
+      <c r="BN180">
+        <v>1.56</v>
+      </c>
+      <c r="BO180">
+        <v>2.9</v>
+      </c>
+      <c r="BP180">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="310">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,9 @@
     <t>['45+2', '65', '75']</t>
   </si>
   <si>
+    <t>['6', '13', '31', '86']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1302,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1764,7 +1767,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2588,7 +2591,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2794,7 +2797,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3000,7 +3003,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3206,7 +3209,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3412,7 +3415,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3618,7 +3621,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3699,7 +3702,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ12">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3824,7 +3827,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4030,7 +4033,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4236,7 +4239,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4442,7 +4445,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4648,7 +4651,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4854,7 +4857,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5678,7 +5681,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5884,7 +5887,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6090,7 +6093,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6296,7 +6299,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6708,7 +6711,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7326,7 +7329,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7532,7 +7535,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8025,7 +8028,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8150,7 +8153,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8356,7 +8359,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8562,7 +8565,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8768,7 +8771,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9180,7 +9183,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9386,7 +9389,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9798,7 +9801,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9876,7 +9879,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ42">
         <v>1.22</v>
@@ -10004,7 +10007,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10210,7 +10213,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10622,7 +10625,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10700,7 +10703,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ46">
         <v>1.11</v>
@@ -11115,7 +11118,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ48">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR48">
         <v>1.29</v>
@@ -11240,7 +11243,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11652,7 +11655,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11858,7 +11861,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12064,7 +12067,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12682,7 +12685,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12888,7 +12891,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13300,7 +13303,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13506,7 +13509,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13712,7 +13715,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13790,7 +13793,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -13918,7 +13921,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14124,7 +14127,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14330,7 +14333,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14536,7 +14539,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14948,7 +14951,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15029,7 +15032,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ67">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR67">
         <v>1.89</v>
@@ -15360,7 +15363,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15566,7 +15569,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15772,7 +15775,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16390,7 +16393,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16674,7 +16677,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ75">
         <v>1.11</v>
@@ -17008,7 +17011,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17214,7 +17217,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17626,7 +17629,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17832,7 +17835,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18038,7 +18041,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18244,7 +18247,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18325,7 +18328,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ83">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR83">
         <v>1.37</v>
@@ -18656,7 +18659,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18862,7 +18865,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19068,7 +19071,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19274,7 +19277,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19892,7 +19895,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20098,7 +20101,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20716,7 +20719,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20922,7 +20925,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21540,7 +21543,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21618,7 +21621,7 @@
         <v>2.2</v>
       </c>
       <c r="AP99">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ99">
         <v>2.18</v>
@@ -21952,7 +21955,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22158,7 +22161,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22364,7 +22367,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22776,7 +22779,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23188,7 +23191,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23475,7 +23478,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ108">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23806,7 +23809,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24012,7 +24015,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24424,7 +24427,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24836,7 +24839,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25042,7 +25045,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25248,7 +25251,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25532,7 +25535,7 @@
         <v>0.4</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ118">
         <v>0.5600000000000001</v>
@@ -25660,7 +25663,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25741,7 +25744,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ119">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR119">
         <v>1.31</v>
@@ -26072,7 +26075,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26278,7 +26281,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26896,7 +26899,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27102,7 +27105,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27308,7 +27311,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27514,7 +27517,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27592,7 +27595,7 @@
         <v>2</v>
       </c>
       <c r="AP128">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ128">
         <v>1.5</v>
@@ -27926,7 +27929,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28750,7 +28753,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29655,7 +29658,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ138">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR138">
         <v>1.3</v>
@@ -30192,7 +30195,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30810,7 +30813,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31016,7 +31019,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31222,7 +31225,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31634,7 +31637,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32252,7 +32255,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32536,7 +32539,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ152">
         <v>0.5</v>
@@ -32664,7 +32667,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32870,7 +32873,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33282,7 +33285,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33488,7 +33491,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33694,7 +33697,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34106,7 +34109,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34312,7 +34315,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34930,7 +34933,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35136,7 +35139,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35342,7 +35345,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35548,7 +35551,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -35832,7 +35835,7 @@
         <v>0.63</v>
       </c>
       <c r="AP168">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ168">
         <v>0.5</v>
@@ -36166,7 +36169,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36578,7 +36581,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36784,7 +36787,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -37814,7 +37817,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38226,7 +38229,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38383,6 +38386,212 @@
       </c>
       <c r="BP180">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7516465</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45677.58333333334</v>
+      </c>
+      <c r="F181">
+        <v>20</v>
+      </c>
+      <c r="G181" t="s">
+        <v>88</v>
+      </c>
+      <c r="H181" t="s">
+        <v>74</v>
+      </c>
+      <c r="I181">
+        <v>3</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>3</v>
+      </c>
+      <c r="L181">
+        <v>4</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="N181">
+        <v>4</v>
+      </c>
+      <c r="O181" t="s">
+        <v>218</v>
+      </c>
+      <c r="P181" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q181">
+        <v>2</v>
+      </c>
+      <c r="R181">
+        <v>2.5</v>
+      </c>
+      <c r="S181">
+        <v>5.5</v>
+      </c>
+      <c r="T181">
+        <v>1.3</v>
+      </c>
+      <c r="U181">
+        <v>3.75</v>
+      </c>
+      <c r="V181">
+        <v>2.4</v>
+      </c>
+      <c r="W181">
+        <v>1.62</v>
+      </c>
+      <c r="X181">
+        <v>5.5</v>
+      </c>
+      <c r="Y181">
+        <v>1.17</v>
+      </c>
+      <c r="Z181">
+        <v>1.48</v>
+      </c>
+      <c r="AA181">
+        <v>4.49</v>
+      </c>
+      <c r="AB181">
+        <v>6.06</v>
+      </c>
+      <c r="AC181">
+        <v>1.03</v>
+      </c>
+      <c r="AD181">
+        <v>17</v>
+      </c>
+      <c r="AE181">
+        <v>1.17</v>
+      </c>
+      <c r="AF181">
+        <v>4.75</v>
+      </c>
+      <c r="AG181">
+        <v>1.58</v>
+      </c>
+      <c r="AH181">
+        <v>2.33</v>
+      </c>
+      <c r="AI181">
+        <v>1.7</v>
+      </c>
+      <c r="AJ181">
+        <v>2.1</v>
+      </c>
+      <c r="AK181">
+        <v>1.15</v>
+      </c>
+      <c r="AL181">
+        <v>1.22</v>
+      </c>
+      <c r="AM181">
+        <v>2.7</v>
+      </c>
+      <c r="AN181">
+        <v>2</v>
+      </c>
+      <c r="AO181">
+        <v>0.88</v>
+      </c>
+      <c r="AP181">
+        <v>2.1</v>
+      </c>
+      <c r="AQ181">
+        <v>0.78</v>
+      </c>
+      <c r="AR181">
+        <v>1.64</v>
+      </c>
+      <c r="AS181">
+        <v>1.05</v>
+      </c>
+      <c r="AT181">
+        <v>2.69</v>
+      </c>
+      <c r="AU181">
+        <v>5</v>
+      </c>
+      <c r="AV181">
+        <v>4</v>
+      </c>
+      <c r="AW181">
+        <v>8</v>
+      </c>
+      <c r="AX181">
+        <v>9</v>
+      </c>
+      <c r="AY181">
+        <v>14</v>
+      </c>
+      <c r="AZ181">
+        <v>17</v>
+      </c>
+      <c r="BA181">
+        <v>7</v>
+      </c>
+      <c r="BB181">
+        <v>3</v>
+      </c>
+      <c r="BC181">
+        <v>10</v>
+      </c>
+      <c r="BD181">
+        <v>1.35</v>
+      </c>
+      <c r="BE181">
+        <v>7</v>
+      </c>
+      <c r="BF181">
+        <v>3.55</v>
+      </c>
+      <c r="BG181">
+        <v>1.33</v>
+      </c>
+      <c r="BH181">
+        <v>2.95</v>
+      </c>
+      <c r="BI181">
+        <v>1.55</v>
+      </c>
+      <c r="BJ181">
+        <v>2.25</v>
+      </c>
+      <c r="BK181">
+        <v>1.9</v>
+      </c>
+      <c r="BL181">
+        <v>1.79</v>
+      </c>
+      <c r="BM181">
+        <v>2.4</v>
+      </c>
+      <c r="BN181">
+        <v>1.49</v>
+      </c>
+      <c r="BO181">
+        <v>3.05</v>
+      </c>
+      <c r="BP181">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="312">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,9 @@
     <t>['6', '13', '31', '86']</t>
   </si>
   <si>
+    <t>['44', '83']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -944,6 +947,9 @@
   </si>
   <si>
     <t>['69', '71', '74', '90+1']</t>
+  </si>
+  <si>
+    <t>['47']</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1767,7 +1773,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2591,7 +2597,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2797,7 +2803,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2875,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>1.22</v>
@@ -3003,7 +3009,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3209,7 +3215,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3290,7 +3296,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ10">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3415,7 +3421,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3621,7 +3627,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3827,7 +3833,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4033,7 +4039,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4239,7 +4245,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4445,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4651,7 +4657,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4857,7 +4863,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5681,7 +5687,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5887,7 +5893,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6093,7 +6099,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6299,7 +6305,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6711,7 +6717,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7329,7 +7335,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7535,7 +7541,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8153,7 +8159,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8359,7 +8365,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8440,7 +8446,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ35">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8565,7 +8571,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8643,7 +8649,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8771,7 +8777,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9183,7 +9189,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9389,7 +9395,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9801,7 +9807,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10007,7 +10013,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10213,7 +10219,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10294,7 +10300,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ44">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
         <v>2.36</v>
@@ -10497,7 +10503,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>1.11</v>
@@ -10625,7 +10631,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11243,7 +11249,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11655,7 +11661,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11861,7 +11867,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12067,7 +12073,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12685,7 +12691,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12891,7 +12897,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12969,7 +12975,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
         <v>0.67</v>
@@ -13303,7 +13309,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13509,7 +13515,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13590,7 +13596,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ60">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR60">
         <v>1.5</v>
@@ -13715,7 +13721,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13921,7 +13927,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14127,7 +14133,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14333,7 +14339,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14539,7 +14545,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14951,7 +14957,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15363,7 +15369,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15569,7 +15575,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15775,7 +15781,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16393,7 +16399,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16474,7 +16480,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ74">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR74">
         <v>1.58</v>
@@ -17011,7 +17017,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17217,7 +17223,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17629,7 +17635,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17835,7 +17841,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17913,7 +17919,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
         <v>2.18</v>
@@ -18041,7 +18047,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18247,7 +18253,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18659,7 +18665,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18865,7 +18871,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19071,7 +19077,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19277,7 +19283,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19895,7 +19901,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20101,7 +20107,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20719,7 +20725,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20925,7 +20931,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21543,7 +21549,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21827,7 +21833,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>0.5</v>
@@ -21955,7 +21961,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22161,7 +22167,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22367,7 +22373,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22448,7 +22454,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ103">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR103">
         <v>1</v>
@@ -22779,7 +22785,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23191,7 +23197,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23809,7 +23815,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24015,7 +24021,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24427,7 +24433,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24839,7 +24845,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25045,7 +25051,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25123,7 +25129,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
         <v>0.7</v>
@@ -25251,7 +25257,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25663,7 +25669,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25947,7 +25953,7 @@
         <v>0.67</v>
       </c>
       <c r="AP120">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
         <v>0.5</v>
@@ -26075,7 +26081,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26281,7 +26287,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26899,7 +26905,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27105,7 +27111,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27311,7 +27317,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27392,7 +27398,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ127">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR127">
         <v>2</v>
@@ -27517,7 +27523,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27929,7 +27935,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28753,7 +28759,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30070,7 +30076,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ140">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR140">
         <v>1.29</v>
@@ -30195,7 +30201,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30813,7 +30819,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31019,7 +31025,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31225,7 +31231,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31637,7 +31643,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32255,7 +32261,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32667,7 +32673,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32873,7 +32879,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33285,7 +33291,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33491,7 +33497,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33697,7 +33703,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34109,7 +34115,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34187,7 +34193,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ160">
         <v>0.44</v>
@@ -34315,7 +34321,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34396,7 +34402,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ161">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -34933,7 +34939,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35139,7 +35145,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35345,7 +35351,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35551,7 +35557,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -36169,7 +36175,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36581,7 +36587,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36787,7 +36793,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -37817,7 +37823,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38229,7 +38235,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38592,6 +38598,212 @@
       </c>
       <c r="BP181">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7516475</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45681.58333333334</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>76</v>
+      </c>
+      <c r="H182" t="s">
+        <v>85</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182">
+        <v>2</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>3</v>
+      </c>
+      <c r="O182" t="s">
+        <v>219</v>
+      </c>
+      <c r="P182" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q182">
+        <v>2.1</v>
+      </c>
+      <c r="R182">
+        <v>2.25</v>
+      </c>
+      <c r="S182">
+        <v>4.75</v>
+      </c>
+      <c r="T182">
+        <v>1.33</v>
+      </c>
+      <c r="U182">
+        <v>3.1</v>
+      </c>
+      <c r="V182">
+        <v>2.45</v>
+      </c>
+      <c r="W182">
+        <v>1.48</v>
+      </c>
+      <c r="X182">
+        <v>5.75</v>
+      </c>
+      <c r="Y182">
+        <v>1.1</v>
+      </c>
+      <c r="Z182">
+        <v>1.64</v>
+      </c>
+      <c r="AA182">
+        <v>4.11</v>
+      </c>
+      <c r="AB182">
+        <v>4.72</v>
+      </c>
+      <c r="AC182">
+        <v>1.05</v>
+      </c>
+      <c r="AD182">
+        <v>13</v>
+      </c>
+      <c r="AE182">
+        <v>1.22</v>
+      </c>
+      <c r="AF182">
+        <v>4.12</v>
+      </c>
+      <c r="AG182">
+        <v>1.75</v>
+      </c>
+      <c r="AH182">
+        <v>2.03</v>
+      </c>
+      <c r="AI182">
+        <v>1.73</v>
+      </c>
+      <c r="AJ182">
+        <v>2</v>
+      </c>
+      <c r="AK182">
+        <v>1.17</v>
+      </c>
+      <c r="AL182">
+        <v>1.2</v>
+      </c>
+      <c r="AM182">
+        <v>2.15</v>
+      </c>
+      <c r="AN182">
+        <v>1.89</v>
+      </c>
+      <c r="AO182">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP182">
+        <v>2</v>
+      </c>
+      <c r="AQ182">
+        <v>0.5</v>
+      </c>
+      <c r="AR182">
+        <v>1.49</v>
+      </c>
+      <c r="AS182">
+        <v>1.09</v>
+      </c>
+      <c r="AT182">
+        <v>2.58</v>
+      </c>
+      <c r="AU182">
+        <v>4</v>
+      </c>
+      <c r="AV182">
+        <v>4</v>
+      </c>
+      <c r="AW182">
+        <v>12</v>
+      </c>
+      <c r="AX182">
+        <v>9</v>
+      </c>
+      <c r="AY182">
+        <v>21</v>
+      </c>
+      <c r="AZ182">
+        <v>15</v>
+      </c>
+      <c r="BA182">
+        <v>7</v>
+      </c>
+      <c r="BB182">
+        <v>2</v>
+      </c>
+      <c r="BC182">
+        <v>9</v>
+      </c>
+      <c r="BD182">
+        <v>1.47</v>
+      </c>
+      <c r="BE182">
+        <v>6.75</v>
+      </c>
+      <c r="BF182">
+        <v>3.05</v>
+      </c>
+      <c r="BG182">
+        <v>1.36</v>
+      </c>
+      <c r="BH182">
+        <v>2.8</v>
+      </c>
+      <c r="BI182">
+        <v>1.63</v>
+      </c>
+      <c r="BJ182">
+        <v>2.12</v>
+      </c>
+      <c r="BK182">
+        <v>2</v>
+      </c>
+      <c r="BL182">
+        <v>1.71</v>
+      </c>
+      <c r="BM182">
+        <v>2.55</v>
+      </c>
+      <c r="BN182">
+        <v>1.44</v>
+      </c>
+      <c r="BO182">
+        <v>3.3</v>
+      </c>
+      <c r="BP182">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
